--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/7_eight_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_4_bus.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/7_eight_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_4_bus.xlsx
@@ -824,22 +824,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.076309581697509</v>
+        <v>1.076309581697511</v>
       </c>
       <c r="O2">
-        <v>0.3968725684451615</v>
+        <v>0.3968725684451628</v>
       </c>
       <c r="P2">
-        <v>0.857503166648942</v>
+        <v>0.8575031666489451</v>
       </c>
       <c r="Q2">
-        <v>8.789108950209561</v>
+        <v>8.789108950209545</v>
       </c>
       <c r="R2">
-        <v>-124.0274590207981</v>
+        <v>-124.0274590207977</v>
       </c>
       <c r="S2">
-        <v>168.9429116866489</v>
+        <v>168.9429116866488</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -883,22 +883,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.044105714997498</v>
+        <v>1.0441057149975</v>
       </c>
       <c r="O3">
-        <v>0.2604212734074335</v>
+        <v>0.2604212734074348</v>
       </c>
       <c r="P3">
-        <v>0.8710642653707239</v>
+        <v>0.8710642653707272</v>
       </c>
       <c r="Q3">
-        <v>5.325452027459456</v>
+        <v>5.325452027459428</v>
       </c>
       <c r="R3">
-        <v>-131.9071155621092</v>
+        <v>-131.9071155621087</v>
       </c>
       <c r="S3">
-        <v>173.6125839687829</v>
+        <v>173.6125839687827</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -942,22 +942,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.044105714978374</v>
+        <v>1.044105714978376</v>
       </c>
       <c r="O4">
-        <v>0.2604212734211524</v>
+        <v>0.2604212734211538</v>
       </c>
       <c r="P4">
-        <v>0.8710642653956977</v>
+        <v>0.8710642653957011</v>
       </c>
       <c r="Q4">
-        <v>5.32545202914839</v>
+        <v>5.32545202914836</v>
       </c>
       <c r="R4">
-        <v>-131.9071155464532</v>
+        <v>-131.9071155464526</v>
       </c>
       <c r="S4">
-        <v>173.612583967056</v>
+        <v>173.6125839670558</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1001,22 +1001,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1.044105714978374</v>
+        <v>1.044105714978376</v>
       </c>
       <c r="O5">
-        <v>0.2604212734211525</v>
+        <v>0.2604212734211538</v>
       </c>
       <c r="P5">
-        <v>0.8710642653956977</v>
+        <v>0.871064265395701</v>
       </c>
       <c r="Q5">
-        <v>5.325452029148392</v>
+        <v>5.325452029148365</v>
       </c>
       <c r="R5">
-        <v>-131.9071155464532</v>
+        <v>-131.9071155464526</v>
       </c>
       <c r="S5">
-        <v>173.612583967056</v>
+        <v>173.6125839670558</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1027,55 +1027,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>1.823703257666274</v>
+        <v>1.823703257666271</v>
       </c>
       <c r="D6">
-        <v>1.823703257666274</v>
+        <v>1.823703257666271</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>21.05831133471241</v>
+        <v>21.05831133471238</v>
       </c>
       <c r="G6">
-        <v>21.05831133471241</v>
+        <v>21.05831133471238</v>
       </c>
       <c r="H6">
-        <v>5.424025632034074</v>
+        <v>4.144030571481082</v>
       </c>
       <c r="I6">
-        <v>6.488939310918615</v>
+        <v>5.855913331295391</v>
       </c>
       <c r="J6">
-        <v>2.237816431607153</v>
+        <v>2.237816431607152</v>
       </c>
       <c r="K6">
-        <v>5.601194464564824</v>
+        <v>5.601194464564855</v>
       </c>
       <c r="L6">
-        <v>2.237816431580073</v>
+        <v>2.237816431580077</v>
       </c>
       <c r="M6">
-        <v>5.601194464517769</v>
+        <v>5.60119446451777</v>
       </c>
       <c r="N6">
-        <v>0.9526279648094349</v>
+        <v>0.9526279648094376</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.9526279648098408</v>
+        <v>0.9526279648098431</v>
       </c>
       <c r="Q6">
-        <v>-2.299257361950802E-13</v>
+        <v>-2.63944979931935E-13</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.999999999992</v>
+        <v>179.9999999999919</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1119,22 +1119,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1.044105714816402</v>
+        <v>1.044105714816404</v>
       </c>
       <c r="O7">
-        <v>0.2604212731841036</v>
+        <v>0.2604212731841052</v>
       </c>
       <c r="P7">
-        <v>0.8710642655544111</v>
+        <v>0.8710642655544143</v>
       </c>
       <c r="Q7">
-        <v>5.32545202917924</v>
+        <v>5.325452029179218</v>
       </c>
       <c r="R7">
-        <v>-131.9071154978766</v>
+        <v>-131.907115497876</v>
       </c>
       <c r="S7">
-        <v>173.6125839691826</v>
+        <v>173.6125839691824</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1178,22 +1178,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>1.044105714816402</v>
+        <v>1.044105714816404</v>
       </c>
       <c r="O8">
-        <v>0.2604212731841039</v>
+        <v>0.2604212731841051</v>
       </c>
       <c r="P8">
-        <v>0.8710642655544111</v>
+        <v>0.8710642655544142</v>
       </c>
       <c r="Q8">
-        <v>5.32545202917925</v>
+        <v>5.325452029179218</v>
       </c>
       <c r="R8">
-        <v>-131.9071154978765</v>
+        <v>-131.907115497876</v>
       </c>
       <c r="S8">
-        <v>173.6125839691826</v>
+        <v>173.6125839691824</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1237,22 +1237,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9526279646173128</v>
+        <v>0.9526279646173152</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.9526279650019631</v>
+        <v>0.9526279650019653</v>
       </c>
       <c r="Q9">
-        <v>1.161115858120931E-09</v>
+        <v>1.161074128441761E-09</v>
       </c>
       <c r="R9">
         <v>0</v>
       </c>
       <c r="S9">
-        <v>179.9999999988307</v>
+        <v>179.9999999988306</v>
       </c>
     </row>
   </sheetData>
@@ -1365,22 +1365,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.105984389062563</v>
+        <v>1.105984389062562</v>
       </c>
       <c r="O2">
-        <v>0.666663779019942</v>
+        <v>0.6666637790199431</v>
       </c>
       <c r="P2">
-        <v>0.9022299634541986</v>
+        <v>0.9022299634541987</v>
       </c>
       <c r="Q2">
-        <v>16.57809355178733</v>
+        <v>16.57809355178736</v>
       </c>
       <c r="R2">
-        <v>-108.7929438266823</v>
+        <v>-108.7929438266822</v>
       </c>
       <c r="S2">
-        <v>159.5275221691293</v>
+        <v>159.5275221691292</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1427,19 +1427,19 @@
         <v>1.085364253791841</v>
       </c>
       <c r="O3">
-        <v>0.5754536980987548</v>
+        <v>0.5754536980987563</v>
       </c>
       <c r="P3">
-        <v>0.8958560121999107</v>
+        <v>0.8958560121999111</v>
       </c>
       <c r="Q3">
-        <v>14.42238148354708</v>
+        <v>14.42238148354711</v>
       </c>
       <c r="R3">
-        <v>-110.0262111070278</v>
+        <v>-110.0262111070277</v>
       </c>
       <c r="S3">
-        <v>162.4369087610724</v>
+        <v>162.4369087610723</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1486,19 +1486,19 @@
         <v>1.085364253779742</v>
       </c>
       <c r="O4">
-        <v>0.5754536981178853</v>
+        <v>0.5754536981178869</v>
       </c>
       <c r="P4">
-        <v>0.8958560122207133</v>
+        <v>0.8958560122207136</v>
       </c>
       <c r="Q4">
-        <v>14.42238148459753</v>
+        <v>14.42238148459756</v>
       </c>
       <c r="R4">
-        <v>-110.0262111027996</v>
+        <v>-110.0262111027995</v>
       </c>
       <c r="S4">
-        <v>162.4369087604029</v>
+        <v>162.4369087604028</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1545,19 +1545,19 @@
         <v>1.085364253779742</v>
       </c>
       <c r="O5">
-        <v>0.5754536981178853</v>
+        <v>0.5754536981178867</v>
       </c>
       <c r="P5">
-        <v>0.8958560122207134</v>
+        <v>0.8958560122207136</v>
       </c>
       <c r="Q5">
-        <v>14.42238148459753</v>
+        <v>14.42238148459755</v>
       </c>
       <c r="R5">
-        <v>-110.0262111027996</v>
+        <v>-110.0262111027995</v>
       </c>
       <c r="S5">
-        <v>162.4369087604029</v>
+        <v>162.4369087604028</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1568,10 +1568,10 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>1.172096236067255</v>
+        <v>1.172096236067254</v>
       </c>
       <c r="D6">
-        <v>1.172096236067255</v>
+        <v>1.172096236067254</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1583,40 +1583,40 @@
         <v>13.53420154819153</v>
       </c>
       <c r="H6">
-        <v>5.424025632034033</v>
+        <v>4.144030571481053</v>
       </c>
       <c r="I6">
-        <v>6.488939310918609</v>
+        <v>5.855913331295389</v>
       </c>
       <c r="J6">
-        <v>2.237816431607131</v>
+        <v>2.237816431607153</v>
       </c>
       <c r="K6">
-        <v>5.601194464564823</v>
+        <v>5.601194464564863</v>
       </c>
       <c r="L6">
-        <v>2.237816431580051</v>
+        <v>2.23781643158009</v>
       </c>
       <c r="M6">
-        <v>5.601194464517764</v>
+        <v>5.601194464517768</v>
       </c>
       <c r="N6">
         <v>1.024925070816898</v>
       </c>
       <c r="O6">
-        <v>0.4143985983631069</v>
+        <v>0.4143985983631085</v>
       </c>
       <c r="P6">
         <v>0.9221668921891054</v>
       </c>
       <c r="Q6">
-        <v>11.27752546015155</v>
+        <v>11.27752546015158</v>
       </c>
       <c r="R6">
-        <v>-104.679650256468</v>
+        <v>-104.6796502564679</v>
       </c>
       <c r="S6">
-        <v>167.4463828994341</v>
+        <v>167.446382899434</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1660,22 +1660,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1.085364253680383</v>
+        <v>1.085364253680382</v>
       </c>
       <c r="O7">
-        <v>0.5754536980076312</v>
+        <v>0.5754536980076329</v>
       </c>
       <c r="P7">
-        <v>0.8958560123056806</v>
+        <v>0.8958560123056809</v>
       </c>
       <c r="Q7">
-        <v>14.4223814846665</v>
+        <v>14.42238148466654</v>
       </c>
       <c r="R7">
-        <v>-110.0262110863364</v>
+        <v>-110.0262110863363</v>
       </c>
       <c r="S7">
-        <v>162.4369087636981</v>
+        <v>162.436908763698</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -1719,22 +1719,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>1.085364253680383</v>
+        <v>1.085364253680382</v>
       </c>
       <c r="O8">
-        <v>0.5754536980076312</v>
+        <v>0.5754536980076328</v>
       </c>
       <c r="P8">
-        <v>0.8958560123056806</v>
+        <v>0.8958560123056809</v>
       </c>
       <c r="Q8">
-        <v>14.4223814846665</v>
+        <v>14.42238148466652</v>
       </c>
       <c r="R8">
-        <v>-110.0262110863364</v>
+        <v>-110.0262110863363</v>
       </c>
       <c r="S8">
-        <v>162.4369087636981</v>
+        <v>162.436908763698</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1781,19 +1781,19 @@
         <v>1.024925070699733</v>
       </c>
       <c r="O9">
-        <v>0.4143985982919323</v>
+        <v>0.4143985982919338</v>
       </c>
       <c r="P9">
         <v>0.9221668923033343</v>
       </c>
       <c r="Q9">
-        <v>11.27752546112743</v>
+        <v>11.27752546112745</v>
       </c>
       <c r="R9">
-        <v>-104.6796502252244</v>
+        <v>-104.6796502252243</v>
       </c>
       <c r="S9">
-        <v>167.4463829013832</v>
+        <v>167.4463829013831</v>
       </c>
     </row>
   </sheetData>
@@ -1906,22 +1906,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.105984389062562</v>
+        <v>1.105984389062563</v>
       </c>
       <c r="O2">
-        <v>0.6666637790199429</v>
+        <v>0.6666637790199437</v>
       </c>
       <c r="P2">
-        <v>0.9022299634541977</v>
+        <v>0.9022299634542003</v>
       </c>
       <c r="Q2">
-        <v>16.57809355178738</v>
+        <v>16.57809355178736</v>
       </c>
       <c r="R2">
-        <v>-108.7929438266823</v>
+        <v>-108.7929438266821</v>
       </c>
       <c r="S2">
-        <v>159.5275221691293</v>
+        <v>159.5275221691292</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1968,19 +1968,19 @@
         <v>1.085364253791841</v>
       </c>
       <c r="O3">
-        <v>0.5754536980987559</v>
+        <v>0.5754536980987568</v>
       </c>
       <c r="P3">
-        <v>0.8958560121999098</v>
+        <v>0.8958560121999126</v>
       </c>
       <c r="Q3">
-        <v>14.42238148354713</v>
+        <v>14.4223814835471</v>
       </c>
       <c r="R3">
-        <v>-110.0262111070278</v>
+        <v>-110.0262111070276</v>
       </c>
       <c r="S3">
-        <v>162.4369087610724</v>
+        <v>162.4369087610723</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2027,16 +2027,16 @@
         <v>1.085364253779742</v>
       </c>
       <c r="O4">
-        <v>0.5754536981178863</v>
+        <v>0.5754536981178874</v>
       </c>
       <c r="P4">
-        <v>0.8958560122207124</v>
+        <v>0.8958560122207153</v>
       </c>
       <c r="Q4">
-        <v>14.42238148459757</v>
+        <v>14.42238148459755</v>
       </c>
       <c r="R4">
-        <v>-110.0262111027996</v>
+        <v>-110.0262111027994</v>
       </c>
       <c r="S4">
         <v>162.4369087604028</v>
@@ -2086,16 +2086,16 @@
         <v>1.085364253779742</v>
       </c>
       <c r="O5">
-        <v>0.5754536981178863</v>
+        <v>0.5754536981178873</v>
       </c>
       <c r="P5">
-        <v>0.8958560122207124</v>
+        <v>0.8958560122207151</v>
       </c>
       <c r="Q5">
-        <v>14.42238148459757</v>
+        <v>14.42238148459754</v>
       </c>
       <c r="R5">
-        <v>-110.0262111027996</v>
+        <v>-110.0262111027994</v>
       </c>
       <c r="S5">
         <v>162.4369087604028</v>
@@ -2109,55 +2109,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>1.172096236067254</v>
+        <v>1.172096236067252</v>
       </c>
       <c r="D6">
-        <v>1.172096236067254</v>
+        <v>1.172096236067252</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>13.53420154819153</v>
+        <v>13.53420154819151</v>
       </c>
       <c r="G6">
-        <v>13.53420154819153</v>
+        <v>13.53420154819151</v>
       </c>
       <c r="H6">
-        <v>5.424025632034074</v>
+        <v>4.144030571481082</v>
       </c>
       <c r="I6">
-        <v>6.488939310918615</v>
+        <v>5.855913331295391</v>
       </c>
       <c r="J6">
-        <v>2.237816431607153</v>
+        <v>2.237816431607152</v>
       </c>
       <c r="K6">
-        <v>5.601194464564824</v>
+        <v>5.601194464564855</v>
       </c>
       <c r="L6">
-        <v>2.237816431580073</v>
+        <v>2.237816431580077</v>
       </c>
       <c r="M6">
-        <v>5.601194464517769</v>
+        <v>5.60119446451777</v>
       </c>
       <c r="N6">
         <v>1.024925070816898</v>
       </c>
       <c r="O6">
-        <v>0.414398598363108</v>
+        <v>0.4143985983631094</v>
       </c>
       <c r="P6">
-        <v>0.9221668921891044</v>
+        <v>0.9221668921891067</v>
       </c>
       <c r="Q6">
-        <v>11.27752546015161</v>
+        <v>11.27752546015158</v>
       </c>
       <c r="R6">
-        <v>-104.679650256468</v>
+        <v>-104.6796502564678</v>
       </c>
       <c r="S6">
-        <v>167.4463828994341</v>
+        <v>167.446382899434</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2201,22 +2201,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1.08536425367565</v>
+        <v>1.085364253675651</v>
       </c>
       <c r="O7">
-        <v>0.575453698002382</v>
+        <v>0.5754536980023831</v>
       </c>
       <c r="P7">
-        <v>0.8958560123097257</v>
+        <v>0.8958560123097286</v>
       </c>
       <c r="Q7">
-        <v>14.42238148466984</v>
+        <v>14.42238148466981</v>
       </c>
       <c r="R7">
-        <v>-110.0262110855524</v>
+        <v>-110.0262110855522</v>
       </c>
       <c r="S7">
-        <v>162.436908763855</v>
+        <v>162.4369087638549</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2260,22 +2260,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>1.08536425367565</v>
+        <v>1.085364253675651</v>
       </c>
       <c r="O8">
-        <v>0.5754536980023822</v>
+        <v>0.5754536980023831</v>
       </c>
       <c r="P8">
-        <v>0.8958560123097258</v>
+        <v>0.8958560123097284</v>
       </c>
       <c r="Q8">
-        <v>14.42238148466984</v>
+        <v>14.4223814846698</v>
       </c>
       <c r="R8">
-        <v>-110.0262110855524</v>
+        <v>-110.0262110855522</v>
       </c>
       <c r="S8">
-        <v>162.436908763855</v>
+        <v>162.4369087638549</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2319,22 +2319,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1.024925070694153</v>
+        <v>1.024925070694154</v>
       </c>
       <c r="O9">
-        <v>0.414398598288544</v>
+        <v>0.4143985982885453</v>
       </c>
       <c r="P9">
-        <v>0.9221668923087727</v>
+        <v>0.922166892308775</v>
       </c>
       <c r="Q9">
-        <v>11.27752546117395</v>
+        <v>11.27752546117392</v>
       </c>
       <c r="R9">
-        <v>-104.6796502237366</v>
+        <v>-104.6796502237364</v>
       </c>
       <c r="S9">
-        <v>167.446382901476</v>
+        <v>167.4463829014759</v>
       </c>
     </row>
   </sheetData>
@@ -2447,22 +2447,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.038230514195722</v>
+        <v>1.03823051419572</v>
       </c>
       <c r="O2">
-        <v>0.4986603516019533</v>
+        <v>0.4986603516019539</v>
       </c>
       <c r="P2">
-        <v>0.739194475446264</v>
+        <v>0.7391944754462626</v>
       </c>
       <c r="Q2">
-        <v>10.91142931169907</v>
+        <v>10.91142931169909</v>
       </c>
       <c r="R2">
-        <v>-127.9801517752528</v>
+        <v>-127.9801517752527</v>
       </c>
       <c r="S2">
-        <v>164.5814748093465</v>
+        <v>164.5814748093464</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -2506,16 +2506,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9918501269914163</v>
+        <v>0.9918501269914149</v>
       </c>
       <c r="O3">
-        <v>0.3451994260358935</v>
+        <v>0.3451994260358942</v>
       </c>
       <c r="P3">
-        <v>0.7588245169091244</v>
+        <v>0.7588245169091223</v>
       </c>
       <c r="Q3">
-        <v>7.308913743474611</v>
+        <v>7.308913743474645</v>
       </c>
       <c r="R3">
         <v>-133.0240089403622</v>
@@ -2565,16 +2565,16 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9918501269686247</v>
+        <v>0.9918501269686232</v>
       </c>
       <c r="O4">
-        <v>0.3451994260642949</v>
+        <v>0.3451994260642958</v>
       </c>
       <c r="P4">
-        <v>0.7588245169453751</v>
+        <v>0.7588245169453731</v>
       </c>
       <c r="Q4">
-        <v>7.308913746347433</v>
+        <v>7.308913746347473</v>
       </c>
       <c r="R4">
         <v>-133.0240089228248</v>
@@ -2624,16 +2624,16 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9918501269686247</v>
+        <v>0.9918501269686234</v>
       </c>
       <c r="O5">
-        <v>0.3451994260642949</v>
+        <v>0.3451994260642957</v>
       </c>
       <c r="P5">
-        <v>0.7588245169453751</v>
+        <v>0.7588245169453731</v>
       </c>
       <c r="Q5">
-        <v>7.308913746347435</v>
+        <v>7.308913746347477</v>
       </c>
       <c r="R5">
         <v>-133.0240089228248</v>
@@ -2665,34 +2665,34 @@
         <v>15.70647566188361</v>
       </c>
       <c r="H6">
-        <v>10.07160052779999</v>
+        <v>7.614010012989719</v>
       </c>
       <c r="I6">
-        <v>7.079996444822623</v>
+        <v>6.446970466441317</v>
       </c>
       <c r="J6">
-        <v>3.953518728206193</v>
+        <v>3.953518728206214</v>
       </c>
       <c r="K6">
-        <v>6.198216755282932</v>
+        <v>6.198216755282955</v>
       </c>
       <c r="L6">
-        <v>3.953518728223953</v>
+        <v>3.953518728224016</v>
       </c>
       <c r="M6">
-        <v>6.19821675531351</v>
+        <v>6.198216755313494</v>
       </c>
       <c r="N6">
-        <v>0.8660254037871229</v>
+        <v>0.8660254037871213</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.8660254037860876</v>
+        <v>0.8660254037860857</v>
       </c>
       <c r="Q6">
-        <v>2.956377078145761E-11</v>
+        <v>2.959973610869657E-11</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2742,16 +2742,16 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9918501268310792</v>
+        <v>0.9918501268310778</v>
       </c>
       <c r="O7">
-        <v>0.3451994258389101</v>
+        <v>0.3451994258389109</v>
       </c>
       <c r="P7">
-        <v>0.7588245170738938</v>
+        <v>0.7588245170738916</v>
       </c>
       <c r="Q7">
-        <v>7.308913745730738</v>
+        <v>7.308913745730776</v>
       </c>
       <c r="R7">
         <v>-133.0240088964073</v>
@@ -2801,16 +2801,16 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9918501268310792</v>
+        <v>0.9918501268310778</v>
       </c>
       <c r="O8">
-        <v>0.3451994258389099</v>
+        <v>0.3451994258389109</v>
       </c>
       <c r="P8">
-        <v>0.7588245170738938</v>
+        <v>0.7588245170738918</v>
       </c>
       <c r="Q8">
-        <v>7.308913745730734</v>
+        <v>7.30891374573078</v>
       </c>
       <c r="R8">
         <v>-133.0240088964073</v>
@@ -2860,16 +2860,16 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8660254036120051</v>
+        <v>0.8660254036120035</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.8660254039612054</v>
+        <v>0.8660254039612035</v>
       </c>
       <c r="Q9">
-        <v>1.193964839869443E-09</v>
+        <v>1.1940008051968E-09</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -2988,22 +2988,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.038230514195722</v>
+        <v>1.03823051419572</v>
       </c>
       <c r="O2">
-        <v>0.4986603516019533</v>
+        <v>0.4986603516019539</v>
       </c>
       <c r="P2">
-        <v>0.739194475446264</v>
+        <v>0.7391944754462626</v>
       </c>
       <c r="Q2">
-        <v>10.91142931169907</v>
+        <v>10.91142931169909</v>
       </c>
       <c r="R2">
-        <v>-127.9801517752528</v>
+        <v>-127.9801517752527</v>
       </c>
       <c r="S2">
-        <v>164.5814748093465</v>
+        <v>164.5814748093464</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -3047,16 +3047,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9918501269914163</v>
+        <v>0.9918501269914149</v>
       </c>
       <c r="O3">
-        <v>0.3451994260358935</v>
+        <v>0.3451994260358942</v>
       </c>
       <c r="P3">
-        <v>0.7588245169091244</v>
+        <v>0.7588245169091223</v>
       </c>
       <c r="Q3">
-        <v>7.308913743474611</v>
+        <v>7.308913743474645</v>
       </c>
       <c r="R3">
         <v>-133.0240089403622</v>
@@ -3106,16 +3106,16 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9918501269686247</v>
+        <v>0.9918501269686232</v>
       </c>
       <c r="O4">
-        <v>0.3451994260642949</v>
+        <v>0.3451994260642958</v>
       </c>
       <c r="P4">
-        <v>0.7588245169453751</v>
+        <v>0.7588245169453731</v>
       </c>
       <c r="Q4">
-        <v>7.308913746347433</v>
+        <v>7.308913746347473</v>
       </c>
       <c r="R4">
         <v>-133.0240089228248</v>
@@ -3165,16 +3165,16 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9918501269686247</v>
+        <v>0.9918501269686234</v>
       </c>
       <c r="O5">
-        <v>0.3451994260642949</v>
+        <v>0.3451994260642957</v>
       </c>
       <c r="P5">
-        <v>0.7588245169453751</v>
+        <v>0.7588245169453731</v>
       </c>
       <c r="Q5">
-        <v>7.308913746347435</v>
+        <v>7.308913746347477</v>
       </c>
       <c r="R5">
         <v>-133.0240089228248</v>
@@ -3206,34 +3206,34 @@
         <v>15.70647566188361</v>
       </c>
       <c r="H6">
-        <v>10.07160052779999</v>
+        <v>7.614010012989719</v>
       </c>
       <c r="I6">
-        <v>7.079996444822623</v>
+        <v>6.446970466441317</v>
       </c>
       <c r="J6">
-        <v>3.953518728206193</v>
+        <v>3.953518728206214</v>
       </c>
       <c r="K6">
-        <v>6.198216755282932</v>
+        <v>6.198216755282955</v>
       </c>
       <c r="L6">
-        <v>3.953518728223953</v>
+        <v>3.953518728224016</v>
       </c>
       <c r="M6">
-        <v>6.19821675531351</v>
+        <v>6.198216755313494</v>
       </c>
       <c r="N6">
-        <v>0.8660254037871229</v>
+        <v>0.8660254037871213</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.8660254037860876</v>
+        <v>0.8660254037860857</v>
       </c>
       <c r="Q6">
-        <v>2.956377078145761E-11</v>
+        <v>2.959973610869657E-11</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -3283,16 +3283,16 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9918501268310792</v>
+        <v>0.9918501268310778</v>
       </c>
       <c r="O7">
-        <v>0.3451994258389101</v>
+        <v>0.3451994258389109</v>
       </c>
       <c r="P7">
-        <v>0.7588245170738938</v>
+        <v>0.7588245170738916</v>
       </c>
       <c r="Q7">
-        <v>7.308913745730738</v>
+        <v>7.308913745730776</v>
       </c>
       <c r="R7">
         <v>-133.0240088964073</v>
@@ -3342,16 +3342,16 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9918501268310792</v>
+        <v>0.9918501268310778</v>
       </c>
       <c r="O8">
-        <v>0.3451994258389099</v>
+        <v>0.3451994258389109</v>
       </c>
       <c r="P8">
-        <v>0.7588245170738938</v>
+        <v>0.7588245170738918</v>
       </c>
       <c r="Q8">
-        <v>7.308913745730734</v>
+        <v>7.30891374573078</v>
       </c>
       <c r="R8">
         <v>-133.0240088964073</v>
@@ -3401,16 +3401,16 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8660254036120051</v>
+        <v>0.8660254036120035</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.8660254039612054</v>
+        <v>0.8660254039612035</v>
       </c>
       <c r="Q9">
-        <v>1.193964839869443E-09</v>
+        <v>1.1940008051968E-09</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -3529,22 +3529,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.029673615020864</v>
+        <v>1.029673615020863</v>
       </c>
       <c r="O2">
-        <v>0.6485080549983553</v>
+        <v>0.6485080549983557</v>
       </c>
       <c r="P2">
-        <v>0.8062590124977642</v>
+        <v>0.8062590124977633</v>
       </c>
       <c r="Q2">
-        <v>17.04738134898282</v>
+        <v>17.04738134898284</v>
       </c>
       <c r="R2">
         <v>-111.4179003643405</v>
       </c>
       <c r="S2">
-        <v>158.0129004047472</v>
+        <v>158.0129004047471</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -3588,16 +3588,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9961841591909968</v>
+        <v>0.9961841591909961</v>
       </c>
       <c r="O3">
-        <v>0.5414739855997083</v>
+        <v>0.5414739855997087</v>
       </c>
       <c r="P3">
-        <v>0.8088350632376625</v>
+        <v>0.8088350632376614</v>
       </c>
       <c r="Q3">
-        <v>14.68424123844327</v>
+        <v>14.68424123844329</v>
       </c>
       <c r="R3">
         <v>-111.1354923877622</v>
@@ -3647,19 +3647,19 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9961841591775156</v>
+        <v>0.9961841591775149</v>
       </c>
       <c r="O4">
-        <v>0.5414739856400395</v>
+        <v>0.5414739856400401</v>
       </c>
       <c r="P4">
-        <v>0.8088350632677661</v>
+        <v>0.8088350632677648</v>
       </c>
       <c r="Q4">
-        <v>14.68424124043326</v>
+        <v>14.68424124043329</v>
       </c>
       <c r="R4">
-        <v>-111.1354923811635</v>
+        <v>-111.1354923811636</v>
       </c>
       <c r="S4">
         <v>161.8076671101219</v>
@@ -3706,19 +3706,19 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9961841591775156</v>
+        <v>0.9961841591775149</v>
       </c>
       <c r="O5">
-        <v>0.5414739856400395</v>
+        <v>0.54147398564004</v>
       </c>
       <c r="P5">
-        <v>0.8088350632677661</v>
+        <v>0.808835063267765</v>
       </c>
       <c r="Q5">
-        <v>14.68424124043326</v>
+        <v>14.68424124043329</v>
       </c>
       <c r="R5">
-        <v>-111.1354923811635</v>
+        <v>-111.1354923811636</v>
       </c>
       <c r="S5">
         <v>161.8076671101219</v>
@@ -3747,37 +3747,37 @@
         <v>10.66123775695432</v>
       </c>
       <c r="H6">
-        <v>10.07160052779999</v>
+        <v>7.614010012989719</v>
       </c>
       <c r="I6">
-        <v>7.079996444822623</v>
+        <v>6.446970466441317</v>
       </c>
       <c r="J6">
-        <v>3.953518728206193</v>
+        <v>3.953518728206214</v>
       </c>
       <c r="K6">
-        <v>6.198216755282932</v>
+        <v>6.198216755282955</v>
       </c>
       <c r="L6">
-        <v>3.953518728223953</v>
+        <v>3.953518728224016</v>
       </c>
       <c r="M6">
-        <v>6.19821675531351</v>
+        <v>6.198216755313494</v>
       </c>
       <c r="N6">
-        <v>0.9044714421388739</v>
+        <v>0.9044714421388732</v>
       </c>
       <c r="O6">
-        <v>0.3264324066386929</v>
+        <v>0.3264324066386936</v>
       </c>
       <c r="P6">
-        <v>0.8574441488588769</v>
+        <v>0.8574441488588759</v>
       </c>
       <c r="Q6">
-        <v>10.28278020653306</v>
+        <v>10.2827802065331</v>
       </c>
       <c r="R6">
-        <v>-98.4269559743544</v>
+        <v>-98.42695597435446</v>
       </c>
       <c r="S6">
         <v>169.1465925796016</v>
@@ -3824,16 +3824,16 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9961841590838891</v>
+        <v>0.9961841590838884</v>
       </c>
       <c r="O7">
-        <v>0.5414739855275256</v>
+        <v>0.5414739855275262</v>
       </c>
       <c r="P7">
-        <v>0.8088350633454179</v>
+        <v>0.8088350633454167</v>
       </c>
       <c r="Q7">
-        <v>14.68424124032946</v>
+        <v>14.6842412403295</v>
       </c>
       <c r="R7">
         <v>-111.1354923653206</v>
@@ -3883,16 +3883,16 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9961841590838891</v>
+        <v>0.9961841590838886</v>
       </c>
       <c r="O8">
-        <v>0.5414739855275256</v>
+        <v>0.5414739855275262</v>
       </c>
       <c r="P8">
-        <v>0.8088350633454179</v>
+        <v>0.8088350633454168</v>
       </c>
       <c r="Q8">
-        <v>14.68424124032946</v>
+        <v>14.6842412403295</v>
       </c>
       <c r="R8">
         <v>-111.1354923653206</v>
@@ -3942,19 +3942,19 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9044714420220109</v>
+        <v>0.90447144202201</v>
       </c>
       <c r="O9">
-        <v>0.3264324066106959</v>
+        <v>0.3264324066106968</v>
       </c>
       <c r="P9">
-        <v>0.85744414897682</v>
+        <v>0.857444148976819</v>
       </c>
       <c r="Q9">
-        <v>10.28278020810398</v>
+        <v>10.28278020810402</v>
       </c>
       <c r="R9">
-        <v>-98.42695593270597</v>
+        <v>-98.42695593270601</v>
       </c>
       <c r="S9">
         <v>169.1465925808718</v>
@@ -4070,22 +4070,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.029673615020864</v>
+        <v>1.029673615020863</v>
       </c>
       <c r="O2">
-        <v>0.6485080549983553</v>
+        <v>0.6485080549983557</v>
       </c>
       <c r="P2">
-        <v>0.8062590124977642</v>
+        <v>0.8062590124977633</v>
       </c>
       <c r="Q2">
-        <v>17.04738134898282</v>
+        <v>17.04738134898284</v>
       </c>
       <c r="R2">
         <v>-111.4179003643405</v>
       </c>
       <c r="S2">
-        <v>158.0129004047472</v>
+        <v>158.0129004047471</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -4129,16 +4129,16 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9961841591909968</v>
+        <v>0.9961841591909961</v>
       </c>
       <c r="O3">
-        <v>0.5414739855997083</v>
+        <v>0.5414739855997087</v>
       </c>
       <c r="P3">
-        <v>0.8088350632376625</v>
+        <v>0.8088350632376614</v>
       </c>
       <c r="Q3">
-        <v>14.68424123844327</v>
+        <v>14.68424123844329</v>
       </c>
       <c r="R3">
         <v>-111.1354923877622</v>
@@ -4188,19 +4188,19 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9961841591775156</v>
+        <v>0.9961841591775149</v>
       </c>
       <c r="O4">
-        <v>0.5414739856400395</v>
+        <v>0.5414739856400401</v>
       </c>
       <c r="P4">
-        <v>0.8088350632677661</v>
+        <v>0.8088350632677648</v>
       </c>
       <c r="Q4">
-        <v>14.68424124043326</v>
+        <v>14.68424124043329</v>
       </c>
       <c r="R4">
-        <v>-111.1354923811635</v>
+        <v>-111.1354923811636</v>
       </c>
       <c r="S4">
         <v>161.8076671101219</v>
@@ -4247,19 +4247,19 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9961841591775156</v>
+        <v>0.9961841591775149</v>
       </c>
       <c r="O5">
-        <v>0.5414739856400395</v>
+        <v>0.54147398564004</v>
       </c>
       <c r="P5">
-        <v>0.8088350632677661</v>
+        <v>0.808835063267765</v>
       </c>
       <c r="Q5">
-        <v>14.68424124043326</v>
+        <v>14.68424124043329</v>
       </c>
       <c r="R5">
-        <v>-111.1354923811635</v>
+        <v>-111.1354923811636</v>
       </c>
       <c r="S5">
         <v>161.8076671101219</v>
@@ -4288,37 +4288,37 @@
         <v>10.66123775695432</v>
       </c>
       <c r="H6">
-        <v>10.07160052779999</v>
+        <v>7.614010012989719</v>
       </c>
       <c r="I6">
-        <v>7.079996444822623</v>
+        <v>6.446970466441317</v>
       </c>
       <c r="J6">
-        <v>3.953518728206193</v>
+        <v>3.953518728206214</v>
       </c>
       <c r="K6">
-        <v>6.198216755282932</v>
+        <v>6.198216755282955</v>
       </c>
       <c r="L6">
-        <v>3.953518728223953</v>
+        <v>3.953518728224016</v>
       </c>
       <c r="M6">
-        <v>6.19821675531351</v>
+        <v>6.198216755313494</v>
       </c>
       <c r="N6">
-        <v>0.9044714421388739</v>
+        <v>0.9044714421388732</v>
       </c>
       <c r="O6">
-        <v>0.3264324066386929</v>
+        <v>0.3264324066386936</v>
       </c>
       <c r="P6">
-        <v>0.8574441488588769</v>
+        <v>0.8574441488588759</v>
       </c>
       <c r="Q6">
-        <v>10.28278020653306</v>
+        <v>10.2827802065331</v>
       </c>
       <c r="R6">
-        <v>-98.4269559743544</v>
+        <v>-98.42695597435446</v>
       </c>
       <c r="S6">
         <v>169.1465925796016</v>
@@ -4365,16 +4365,16 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9961841590838891</v>
+        <v>0.9961841590838884</v>
       </c>
       <c r="O7">
-        <v>0.5414739855275256</v>
+        <v>0.5414739855275262</v>
       </c>
       <c r="P7">
-        <v>0.8088350633454179</v>
+        <v>0.8088350633454167</v>
       </c>
       <c r="Q7">
-        <v>14.68424124032946</v>
+        <v>14.6842412403295</v>
       </c>
       <c r="R7">
         <v>-111.1354923653206</v>
@@ -4424,16 +4424,16 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9961841590838891</v>
+        <v>0.9961841590838886</v>
       </c>
       <c r="O8">
-        <v>0.5414739855275256</v>
+        <v>0.5414739855275262</v>
       </c>
       <c r="P8">
-        <v>0.8088350633454179</v>
+        <v>0.8088350633454168</v>
       </c>
       <c r="Q8">
-        <v>14.68424124032946</v>
+        <v>14.6842412403295</v>
       </c>
       <c r="R8">
         <v>-111.1354923653206</v>
@@ -4483,19 +4483,19 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9044714420220109</v>
+        <v>0.90447144202201</v>
       </c>
       <c r="O9">
-        <v>0.3264324066106959</v>
+        <v>0.3264324066106968</v>
       </c>
       <c r="P9">
-        <v>0.85744414897682</v>
+        <v>0.857444148976819</v>
       </c>
       <c r="Q9">
-        <v>10.28278020810398</v>
+        <v>10.28278020810402</v>
       </c>
       <c r="R9">
-        <v>-98.42695593270597</v>
+        <v>-98.42695593270601</v>
       </c>
       <c r="S9">
         <v>169.1465925808718</v>
@@ -4614,22 +4614,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.690704543768849</v>
+        <v>0.6701093554647521</v>
       </c>
       <c r="O2">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P2">
-        <v>0.9165788224953955</v>
+        <v>0.8924054197913458</v>
       </c>
       <c r="Q2">
-        <v>33.87431367069092</v>
+        <v>35.81393605967047</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999666</v>
+        <v>-89.99999999999665</v>
       </c>
       <c r="S2">
-        <v>128.7305819267978</v>
+        <v>127.511662143737</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -4676,22 +4676,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6416038458309423</v>
+        <v>0.623068855046149</v>
       </c>
       <c r="O3">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P3">
-        <v>0.8604910630369526</v>
+        <v>0.8319416047608117</v>
       </c>
       <c r="Q3">
-        <v>38.63048690959413</v>
+        <v>41.37736785042141</v>
       </c>
       <c r="R3">
         <v>-89.99999999999655</v>
       </c>
       <c r="S3">
-        <v>125.6247237392154</v>
+        <v>124.1927576514372</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -4738,22 +4738,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6416038458680837</v>
+        <v>0.6230688550857582</v>
       </c>
       <c r="O4">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P4">
-        <v>0.8604910630311051</v>
+        <v>0.8319416047552866</v>
       </c>
       <c r="Q4">
-        <v>38.63048690994289</v>
+        <v>41.37736785047436</v>
       </c>
       <c r="R4">
         <v>-89.99999999999655</v>
       </c>
       <c r="S4">
-        <v>125.6247237416714</v>
+        <v>124.1927576541387</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -4800,22 +4800,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6416038458680837</v>
+        <v>0.6230688550857583</v>
       </c>
       <c r="O5">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P5">
-        <v>0.8604910630311051</v>
+        <v>0.8319416047552866</v>
       </c>
       <c r="Q5">
-        <v>38.63048690994289</v>
+        <v>41.37736785047436</v>
       </c>
       <c r="R5">
         <v>-89.99999999999655</v>
       </c>
       <c r="S5">
-        <v>125.6247237416714</v>
+        <v>124.1927576541387</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -4826,7 +4826,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>1.879618138992242</v>
+        <v>1.993736822392635</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>21.70396077041748</v>
+        <v>23.02168982203314</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -4844,43 +4844,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>5.424025632034139</v>
+        <v>4.144030571481131</v>
       </c>
       <c r="I6">
-        <v>6.488939310918271</v>
+        <v>5.855913331295038</v>
       </c>
       <c r="J6">
-        <v>2.237816431602246</v>
+        <v>2.237816431602227</v>
       </c>
       <c r="K6">
-        <v>5.601194464517905</v>
+        <v>5.601194464517901</v>
       </c>
       <c r="L6">
-        <v>2.237816431580261</v>
+        <v>2.237816431580251</v>
       </c>
       <c r="M6">
-        <v>5.601194464517699</v>
+        <v>5.601194464517659</v>
       </c>
       <c r="N6">
-        <v>0.616085536883434</v>
+        <v>0.6102204300157394</v>
       </c>
       <c r="O6">
-        <v>1.100000023839115</v>
+        <v>1.100000023838943</v>
       </c>
       <c r="P6">
-        <v>0.7357403471675246</v>
+        <v>0.6988171900027914</v>
       </c>
       <c r="Q6">
-        <v>50.65955129667951</v>
+        <v>54.57987252493232</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999659</v>
       </c>
       <c r="S6">
-        <v>122.061571814924</v>
+        <v>120.4036908160044</v>
       </c>
       <c r="T6">
-        <v>1.879618138992242</v>
+        <v>1.993736822392635</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -4924,22 +4924,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.6416038459380672</v>
+        <v>0.6230688551733712</v>
       </c>
       <c r="O7">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P7">
-        <v>0.8604910628844717</v>
+        <v>0.8319416046009179</v>
       </c>
       <c r="Q7">
-        <v>38.63048692272726</v>
+        <v>41.37736786376646</v>
       </c>
       <c r="R7">
         <v>-89.99999999999655</v>
       </c>
       <c r="S7">
-        <v>125.624723745825</v>
+        <v>124.1927576588802</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -4986,22 +4986,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.6416038459380672</v>
+        <v>0.6230688551733712</v>
       </c>
       <c r="O8">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P8">
-        <v>0.8604910628844717</v>
+        <v>0.8319416046009177</v>
       </c>
       <c r="Q8">
-        <v>38.63048692272726</v>
+        <v>41.37736786376647</v>
       </c>
       <c r="R8">
         <v>-89.99999999999655</v>
       </c>
       <c r="S8">
-        <v>125.624723745825</v>
+        <v>124.1927576588802</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -5048,22 +5048,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.616085537026685</v>
+        <v>0.6102204301813781</v>
       </c>
       <c r="O9">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P9">
-        <v>0.7357403470035909</v>
+        <v>0.6988171898302792</v>
       </c>
       <c r="Q9">
-        <v>50.65955130828237</v>
+        <v>54.57987253570565</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999659</v>
       </c>
       <c r="S9">
-        <v>122.0615718223985</v>
+        <v>120.4036908245411</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -5182,22 +5182,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.6907045437688484</v>
+        <v>0.6701093554647447</v>
       </c>
       <c r="O2">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P2">
-        <v>0.9165788224953982</v>
+        <v>0.8924054197913535</v>
       </c>
       <c r="Q2">
-        <v>33.8743136706907</v>
+        <v>35.81393605966983</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999663</v>
+        <v>-89.99999999999666</v>
       </c>
       <c r="S2">
-        <v>128.7305819267978</v>
+        <v>127.5116621437365</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5244,22 +5244,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6416038458309411</v>
+        <v>0.6230688550461386</v>
       </c>
       <c r="O3">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P3">
-        <v>0.860491063036956</v>
+        <v>0.8319416047608204</v>
       </c>
       <c r="Q3">
-        <v>38.63048690959387</v>
+        <v>41.37736785042078</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S3">
-        <v>125.6247237392154</v>
+        <v>124.1927576514365</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5306,22 +5306,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6416038458680823</v>
+        <v>0.6230688550857481</v>
       </c>
       <c r="O4">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P4">
-        <v>0.8604910630311083</v>
+        <v>0.831941604755295</v>
       </c>
       <c r="Q4">
-        <v>38.63048690994263</v>
+        <v>41.37736785047375</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S4">
-        <v>125.6247237416714</v>
+        <v>124.192757654138</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5368,22 +5368,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.6416038458680823</v>
+        <v>0.6230688550857479</v>
       </c>
       <c r="O5">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P5">
-        <v>0.8604910630311083</v>
+        <v>0.8319416047552949</v>
       </c>
       <c r="Q5">
-        <v>38.63048690994263</v>
+        <v>41.37736785047375</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999653</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S5">
-        <v>125.6247237416714</v>
+        <v>124.192757654138</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5394,7 +5394,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>1.879618138992238</v>
+        <v>1.993736822392633</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -5403,7 +5403,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>21.70396077041744</v>
+        <v>23.02168982203312</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -5412,43 +5412,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>5.42402563203418</v>
+        <v>4.144030571481242</v>
       </c>
       <c r="I6">
-        <v>6.488939310918272</v>
+        <v>5.855913331294972</v>
       </c>
       <c r="J6">
-        <v>2.23781643160227</v>
+        <v>2.237816431602291</v>
       </c>
       <c r="K6">
-        <v>5.601194464517907</v>
+        <v>5.601194464517867</v>
       </c>
       <c r="L6">
-        <v>2.237816431580284</v>
+        <v>2.237816431580311</v>
       </c>
       <c r="M6">
-        <v>5.601194464517697</v>
+        <v>5.60119446451766</v>
       </c>
       <c r="N6">
-        <v>0.6160855368834315</v>
+        <v>0.6102204300157258</v>
       </c>
       <c r="O6">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P6">
-        <v>0.7357403471675286</v>
+        <v>0.6988171900028013</v>
       </c>
       <c r="Q6">
-        <v>50.65955129667925</v>
+        <v>54.57987252493193</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999653</v>
+        <v>-89.9999999999966</v>
       </c>
       <c r="S6">
-        <v>122.0615718149239</v>
+        <v>120.4036908160035</v>
       </c>
       <c r="T6">
-        <v>1.879618138992238</v>
+        <v>1.993736822392633</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -5492,22 +5492,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.6416038459413985</v>
+        <v>0.6230688551775329</v>
       </c>
       <c r="O7">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P7">
-        <v>0.8604910628774926</v>
+        <v>0.8319416045935755</v>
       </c>
       <c r="Q7">
-        <v>38.63048692333578</v>
+        <v>41.3773678643988</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999652</v>
+        <v>-89.99999999999655</v>
       </c>
       <c r="S7">
-        <v>125.6247237460228</v>
+        <v>124.1927576591053</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -5554,22 +5554,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.6416038459413983</v>
+        <v>0.6230688551775327</v>
       </c>
       <c r="O8">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P8">
-        <v>0.8604910628774924</v>
+        <v>0.8319416045935754</v>
       </c>
       <c r="Q8">
-        <v>38.63048692333579</v>
+        <v>41.37736786439881</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999652</v>
+        <v>-89.99999999999656</v>
       </c>
       <c r="S8">
-        <v>125.6247237460228</v>
+        <v>124.1927576591053</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -5616,22 +5616,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.6160855370335041</v>
+        <v>0.610220430189252</v>
       </c>
       <c r="O9">
-        <v>1.100000023839115</v>
+        <v>1.100000023838944</v>
       </c>
       <c r="P9">
-        <v>0.7357403469957886</v>
+        <v>0.6988171898220742</v>
       </c>
       <c r="Q9">
-        <v>50.65955130883461</v>
+        <v>54.57987253621828</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999652</v>
+        <v>-89.9999999999966</v>
       </c>
       <c r="S9">
-        <v>122.0615718227544</v>
+        <v>120.4036908249467</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -5750,22 +5750,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8960969432761648</v>
+        <v>0.8894917685036033</v>
       </c>
       <c r="O2">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P2">
-        <v>1.018847183336919</v>
+        <v>1.013635477355387</v>
       </c>
       <c r="Q2">
-        <v>29.63933702271319</v>
+        <v>29.8411524356338</v>
       </c>
       <c r="R2">
         <v>-89.99999999999655</v>
       </c>
       <c r="S2">
-        <v>139.8572097420366</v>
+        <v>139.567765888999</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -5812,22 +5812,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8660113609881631</v>
+        <v>0.8588810253359987</v>
       </c>
       <c r="O3">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P3">
-        <v>0.9895984646517587</v>
+        <v>0.9832134679654949</v>
       </c>
       <c r="Q3">
-        <v>30.97920348178567</v>
+        <v>31.2757540190857</v>
       </c>
       <c r="R3">
         <v>-89.99999999999649</v>
       </c>
       <c r="S3">
-        <v>138.6148597240778</v>
+        <v>138.2967164729219</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -5874,22 +5874,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.866011361005279</v>
+        <v>0.8588810253538069</v>
       </c>
       <c r="O4">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P4">
-        <v>0.9895984646504469</v>
+        <v>0.9832134679643385</v>
       </c>
       <c r="Q4">
-        <v>30.97920348223673</v>
+        <v>31.27575401953007</v>
       </c>
       <c r="R4">
         <v>-89.99999999999649</v>
       </c>
       <c r="S4">
-        <v>138.6148597251419</v>
+        <v>138.2967164740279</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -5936,22 +5936,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.866011361005279</v>
+        <v>0.8588810253538069</v>
       </c>
       <c r="O5">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P5">
-        <v>0.9895984646504469</v>
+        <v>0.9832134679643385</v>
       </c>
       <c r="Q5">
-        <v>30.97920348223673</v>
+        <v>31.27575401953007</v>
       </c>
       <c r="R5">
         <v>-89.99999999999649</v>
       </c>
       <c r="S5">
-        <v>138.6148597251419</v>
+        <v>138.2967164740279</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -5962,7 +5962,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.9272674540004711</v>
+        <v>0.956936931243072</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -5971,7 +5971,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>10.70716228355902</v>
+        <v>11.04975589701364</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -5980,43 +5980,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>5.424025632034139</v>
+        <v>4.144030571481131</v>
       </c>
       <c r="I6">
-        <v>6.488939310918271</v>
+        <v>5.855913331295038</v>
       </c>
       <c r="J6">
-        <v>2.237816431602246</v>
+        <v>2.237816431602227</v>
       </c>
       <c r="K6">
-        <v>5.601194464517905</v>
+        <v>5.601194464517901</v>
       </c>
       <c r="L6">
-        <v>2.237816431580261</v>
+        <v>2.237816431580251</v>
       </c>
       <c r="M6">
-        <v>5.601194464517699</v>
+        <v>5.601194464517659</v>
       </c>
       <c r="N6">
-        <v>0.8321814670359311</v>
+        <v>0.8253241299356193</v>
       </c>
       <c r="O6">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P6">
-        <v>0.9258054222065151</v>
+        <v>0.9171930367293541</v>
       </c>
       <c r="Q6">
-        <v>34.82090261750643</v>
+        <v>35.32680789369962</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999649</v>
+        <v>-89.99999999999652</v>
       </c>
       <c r="S6">
-        <v>137.5546695821811</v>
+        <v>137.2352165116173</v>
       </c>
       <c r="T6">
-        <v>0.9272674540004711</v>
+        <v>0.956936931243072</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -6060,22 +6060,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.866011361019383</v>
+        <v>0.8588810253700441</v>
       </c>
       <c r="O7">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P7">
-        <v>0.9895984645810181</v>
+        <v>0.9832134678930871</v>
       </c>
       <c r="Q7">
-        <v>30.97920348735336</v>
+        <v>31.27575402483257</v>
       </c>
       <c r="R7">
         <v>-89.99999999999649</v>
       </c>
       <c r="S7">
-        <v>138.6148597272766</v>
+        <v>138.2967164762885</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -6122,22 +6122,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.8660113610193829</v>
+        <v>0.8588810253700441</v>
       </c>
       <c r="O8">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P8">
-        <v>0.9895984645810181</v>
+        <v>0.9832134678930871</v>
       </c>
       <c r="Q8">
-        <v>30.97920348735336</v>
+        <v>31.27575402483257</v>
       </c>
       <c r="R8">
         <v>-89.99999999999649</v>
       </c>
       <c r="S8">
-        <v>138.6148597272766</v>
+        <v>138.2967164762885</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -6184,22 +6184,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8321814670756001</v>
+        <v>0.8253241299787153</v>
       </c>
       <c r="O9">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P9">
-        <v>0.9258054221324425</v>
+        <v>0.9171930366535298</v>
       </c>
       <c r="Q9">
-        <v>34.82090262335212</v>
+        <v>35.32680789971022</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999649</v>
+        <v>-89.99999999999652</v>
       </c>
       <c r="S9">
-        <v>137.554669585734</v>
+        <v>137.2352165153675</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -6535,22 +6535,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8960969432761643</v>
+        <v>0.8894917685036003</v>
       </c>
       <c r="O2">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P2">
-        <v>1.01884718333692</v>
+        <v>1.013635477355388</v>
       </c>
       <c r="Q2">
-        <v>29.63933702271315</v>
+        <v>29.84115243563367</v>
       </c>
       <c r="R2">
         <v>-89.99999999999655</v>
       </c>
       <c r="S2">
-        <v>139.8572097420366</v>
+        <v>139.5677658889988</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -6597,22 +6597,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8660113609881626</v>
+        <v>0.8588810253359952</v>
       </c>
       <c r="O3">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P3">
-        <v>0.9895984646517595</v>
+        <v>0.9832134679654959</v>
       </c>
       <c r="Q3">
-        <v>30.97920348178561</v>
+        <v>31.27575401908557</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999649</v>
       </c>
       <c r="S3">
-        <v>138.6148597240778</v>
+        <v>138.2967164729217</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -6659,22 +6659,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8660113610052785</v>
+        <v>0.8588810253538036</v>
       </c>
       <c r="O4">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P4">
-        <v>0.9895984646504478</v>
+        <v>0.9832134679643395</v>
       </c>
       <c r="Q4">
-        <v>30.97920348223667</v>
+        <v>31.27575401952995</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999649</v>
       </c>
       <c r="S4">
-        <v>138.6148597251418</v>
+        <v>138.2967164740276</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -6721,22 +6721,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8660113610052785</v>
+        <v>0.8588810253538033</v>
       </c>
       <c r="O5">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P5">
-        <v>0.9895984646504478</v>
+        <v>0.9832134679643393</v>
       </c>
       <c r="Q5">
-        <v>30.97920348223667</v>
+        <v>31.27575401952996</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999649</v>
       </c>
       <c r="S5">
-        <v>138.6148597251418</v>
+        <v>138.2967164740276</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.9272674540004698</v>
+        <v>0.9569369312430706</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -6756,7 +6756,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>10.70716228355901</v>
+        <v>11.04975589701362</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -6765,43 +6765,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>5.42402563203418</v>
+        <v>4.144030571481242</v>
       </c>
       <c r="I6">
-        <v>6.488939310918272</v>
+        <v>5.855913331294972</v>
       </c>
       <c r="J6">
-        <v>2.23781643160227</v>
+        <v>2.237816431602291</v>
       </c>
       <c r="K6">
-        <v>5.601194464517907</v>
+        <v>5.601194464517867</v>
       </c>
       <c r="L6">
-        <v>2.237816431580284</v>
+        <v>2.237816431580311</v>
       </c>
       <c r="M6">
-        <v>5.601194464517697</v>
+        <v>5.60119446451766</v>
       </c>
       <c r="N6">
-        <v>0.8321814670359301</v>
+        <v>0.8253241299356152</v>
       </c>
       <c r="O6">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P6">
-        <v>0.925805422206516</v>
+        <v>0.9171930367293555</v>
       </c>
       <c r="Q6">
-        <v>34.82090261750637</v>
+        <v>35.32680789369948</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999652</v>
       </c>
       <c r="S6">
-        <v>137.5546695821811</v>
+        <v>137.235216511617</v>
       </c>
       <c r="T6">
-        <v>0.9272674540004697</v>
+        <v>0.9569369312430706</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -6845,22 +6845,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.8660113610200542</v>
+        <v>0.8588810253708138</v>
       </c>
       <c r="O7">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P7">
-        <v>0.9895984645777127</v>
+        <v>0.9832134678896952</v>
       </c>
       <c r="Q7">
-        <v>30.97920348759696</v>
+        <v>31.27575402508494</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999649</v>
       </c>
       <c r="S7">
-        <v>138.6148597273782</v>
+        <v>138.2967164763959</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -6907,22 +6907,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.866011361020054</v>
+        <v>0.8588810253708137</v>
       </c>
       <c r="O8">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P8">
-        <v>0.9895984645777126</v>
+        <v>0.9832134678896951</v>
       </c>
       <c r="Q8">
-        <v>30.97920348759695</v>
+        <v>31.27575402508495</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999649</v>
       </c>
       <c r="S8">
-        <v>138.6148597273782</v>
+        <v>138.2967164763959</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -6969,22 +6969,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8321814670774883</v>
+        <v>0.8253241299807635</v>
       </c>
       <c r="O9">
-        <v>1.10000002384053</v>
+        <v>1.100000023840483</v>
       </c>
       <c r="P9">
-        <v>0.9258054221289163</v>
+        <v>0.9171930366499204</v>
       </c>
       <c r="Q9">
-        <v>34.82090262363043</v>
+        <v>35.32680789999631</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999648</v>
+        <v>-89.99999999999652</v>
       </c>
       <c r="S9">
-        <v>137.5546695859031</v>
+        <v>137.2352165155458</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -7103,22 +7103,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.6768777152300798</v>
+        <v>0.6464421203948201</v>
       </c>
       <c r="O2">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986957</v>
       </c>
       <c r="P2">
-        <v>0.9227238885629322</v>
+        <v>0.9012412667911193</v>
       </c>
       <c r="Q2">
-        <v>26.62782469006527</v>
+        <v>27.9337282061839</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999672</v>
+        <v>-89.99999999999669</v>
       </c>
       <c r="S2">
-        <v>130.9773355386828</v>
+        <v>129.3243369262347</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7165,22 +7165,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6239309251876199</v>
+        <v>0.5943943024931746</v>
       </c>
       <c r="O3">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986957</v>
       </c>
       <c r="P3">
-        <v>0.8596331470163231</v>
+        <v>0.8315820218503908</v>
       </c>
       <c r="Q3">
-        <v>31.40928562038851</v>
+        <v>33.8265702131776</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S3">
-        <v>128.2763463929966</v>
+        <v>126.4259041360176</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7227,22 +7227,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6239309252392681</v>
+        <v>0.5943943025500217</v>
       </c>
       <c r="O4">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986958</v>
       </c>
       <c r="P4">
-        <v>0.8596331470128097</v>
+        <v>0.8315820218479503</v>
       </c>
       <c r="Q4">
-        <v>31.40928562128463</v>
+        <v>33.82657021366185</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S4">
-        <v>128.2763463964921</v>
+        <v>126.425904139946</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7289,22 +7289,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.623930925239268</v>
+        <v>0.5943943025500218</v>
       </c>
       <c r="O5">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986958</v>
       </c>
       <c r="P5">
-        <v>0.8596331470128098</v>
+        <v>0.8315820218479505</v>
       </c>
       <c r="Q5">
-        <v>31.40928562128463</v>
+        <v>33.82657021366184</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S5">
-        <v>128.2763463964921</v>
+        <v>126.425904139946</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7315,7 +7315,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>1.306917170766398</v>
+        <v>1.418978941797048</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7324,7 +7324,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>15.09097960701049</v>
+        <v>16.38495748041872</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -7333,43 +7333,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>10.07160052780018</v>
+        <v>7.61401001298993</v>
       </c>
       <c r="I6">
-        <v>7.079996444822221</v>
+        <v>6.44697046644081</v>
       </c>
       <c r="J6">
-        <v>3.953518728204021</v>
+        <v>3.953518728204044</v>
       </c>
       <c r="K6">
-        <v>6.198216755313587</v>
+        <v>6.198216755313541</v>
       </c>
       <c r="L6">
-        <v>3.953518728224332</v>
+        <v>3.953518728224347</v>
       </c>
       <c r="M6">
-        <v>6.198216755313418</v>
+        <v>6.198216755313323</v>
       </c>
       <c r="N6">
-        <v>0.5717545054532647</v>
+        <v>0.5587311830649456</v>
       </c>
       <c r="O6">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986958</v>
       </c>
       <c r="P6">
-        <v>0.70476307048793</v>
+        <v>0.6620730627524535</v>
       </c>
       <c r="Q6">
-        <v>46.55389845206196</v>
+        <v>51.4427622661908</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999655</v>
+        <v>-89.9999999999966</v>
       </c>
       <c r="S6">
-        <v>123.9099281709561</v>
+        <v>121.736051118476</v>
       </c>
       <c r="T6">
-        <v>1.306917170766398</v>
+        <v>1.418978941797048</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -7413,22 +7413,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.6239309252611087</v>
+        <v>0.5943943025875941</v>
       </c>
       <c r="O7">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986957</v>
       </c>
       <c r="P7">
-        <v>0.8596331468856179</v>
+        <v>0.8315820217108696</v>
       </c>
       <c r="Q7">
-        <v>31.40928563329063</v>
+        <v>33.82657022705358</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S7">
-        <v>128.2763463989793</v>
+        <v>126.4259041429662</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -7475,22 +7475,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.6239309252611087</v>
+        <v>0.5943943025875942</v>
       </c>
       <c r="O8">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986958</v>
       </c>
       <c r="P8">
-        <v>0.859633146885618</v>
+        <v>0.8315820217108697</v>
       </c>
       <c r="Q8">
-        <v>31.40928563329063</v>
+        <v>33.82657022705357</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S8">
-        <v>128.2763463989793</v>
+        <v>126.4259041429662</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -7537,22 +7537,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.5717545055666681</v>
+        <v>0.5587311832060781</v>
       </c>
       <c r="O9">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986958</v>
       </c>
       <c r="P9">
-        <v>0.7047630703407078</v>
+        <v>0.6620730625943032</v>
       </c>
       <c r="Q9">
-        <v>46.55389846463247</v>
+        <v>51.44276227823361</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999655</v>
+        <v>-89.9999999999966</v>
       </c>
       <c r="S9">
-        <v>123.9099281777197</v>
+        <v>121.7360511265472</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -7671,22 +7671,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.6768777152300798</v>
+        <v>0.6464421203948201</v>
       </c>
       <c r="O2">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986957</v>
       </c>
       <c r="P2">
-        <v>0.9227238885629322</v>
+        <v>0.9012412667911193</v>
       </c>
       <c r="Q2">
-        <v>26.62782469006527</v>
+        <v>27.9337282061839</v>
       </c>
       <c r="R2">
-        <v>-89.99999999999672</v>
+        <v>-89.99999999999669</v>
       </c>
       <c r="S2">
-        <v>130.9773355386828</v>
+        <v>129.3243369262347</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -7733,22 +7733,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.6239309251876199</v>
+        <v>0.5943943024931746</v>
       </c>
       <c r="O3">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986957</v>
       </c>
       <c r="P3">
-        <v>0.8596331470163231</v>
+        <v>0.8315820218503908</v>
       </c>
       <c r="Q3">
-        <v>31.40928562038851</v>
+        <v>33.8265702131776</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S3">
-        <v>128.2763463929966</v>
+        <v>126.4259041360176</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -7795,22 +7795,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.6239309252392681</v>
+        <v>0.5943943025500217</v>
       </c>
       <c r="O4">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986958</v>
       </c>
       <c r="P4">
-        <v>0.8596331470128097</v>
+        <v>0.8315820218479503</v>
       </c>
       <c r="Q4">
-        <v>31.40928562128463</v>
+        <v>33.82657021366185</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S4">
-        <v>128.2763463964921</v>
+        <v>126.425904139946</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -7857,22 +7857,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.623930925239268</v>
+        <v>0.5943943025500218</v>
       </c>
       <c r="O5">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986958</v>
       </c>
       <c r="P5">
-        <v>0.8596331470128098</v>
+        <v>0.8315820218479505</v>
       </c>
       <c r="Q5">
-        <v>31.40928562128463</v>
+        <v>33.82657021366184</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S5">
-        <v>128.2763463964921</v>
+        <v>126.425904139946</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -7883,7 +7883,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>1.306917170766398</v>
+        <v>1.418978941797048</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7892,7 +7892,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>15.09097960701049</v>
+        <v>16.38495748041872</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -7901,43 +7901,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>10.07160052780018</v>
+        <v>7.61401001298993</v>
       </c>
       <c r="I6">
-        <v>7.079996444822221</v>
+        <v>6.44697046644081</v>
       </c>
       <c r="J6">
-        <v>3.953518728204021</v>
+        <v>3.953518728204044</v>
       </c>
       <c r="K6">
-        <v>6.198216755313587</v>
+        <v>6.198216755313541</v>
       </c>
       <c r="L6">
-        <v>3.953518728224332</v>
+        <v>3.953518728224347</v>
       </c>
       <c r="M6">
-        <v>6.198216755313418</v>
+        <v>6.198216755313323</v>
       </c>
       <c r="N6">
-        <v>0.5717545054532647</v>
+        <v>0.5587311830649456</v>
       </c>
       <c r="O6">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986958</v>
       </c>
       <c r="P6">
-        <v>0.70476307048793</v>
+        <v>0.6620730627524535</v>
       </c>
       <c r="Q6">
-        <v>46.55389845206196</v>
+        <v>51.4427622661908</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999655</v>
+        <v>-89.9999999999966</v>
       </c>
       <c r="S6">
-        <v>123.9099281709561</v>
+        <v>121.736051118476</v>
       </c>
       <c r="T6">
-        <v>1.306917170766398</v>
+        <v>1.418978941797048</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -7981,22 +7981,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.6239309252611087</v>
+        <v>0.5943943025875941</v>
       </c>
       <c r="O7">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986957</v>
       </c>
       <c r="P7">
-        <v>0.8596331468856179</v>
+        <v>0.8315820217108696</v>
       </c>
       <c r="Q7">
-        <v>31.40928563329063</v>
+        <v>33.82657022705358</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S7">
-        <v>128.2763463989793</v>
+        <v>126.4259041429662</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -8043,22 +8043,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.6239309252611087</v>
+        <v>0.5943943025875942</v>
       </c>
       <c r="O8">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986958</v>
       </c>
       <c r="P8">
-        <v>0.859633146885618</v>
+        <v>0.8315820217108697</v>
       </c>
       <c r="Q8">
-        <v>31.40928563329063</v>
+        <v>33.82657022705357</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999655</v>
+        <v>-89.99999999999653</v>
       </c>
       <c r="S8">
-        <v>128.2763463989793</v>
+        <v>126.4259041429662</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -8105,22 +8105,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.5717545055666681</v>
+        <v>0.5587311832060781</v>
       </c>
       <c r="O9">
-        <v>0.9999999999989121</v>
+        <v>0.9999999999986958</v>
       </c>
       <c r="P9">
-        <v>0.7047630703407078</v>
+        <v>0.6620730625943032</v>
       </c>
       <c r="Q9">
-        <v>46.55389846463247</v>
+        <v>51.44276227823361</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999655</v>
+        <v>-89.9999999999966</v>
       </c>
       <c r="S9">
-        <v>123.9099281777197</v>
+        <v>121.7360511265472</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -8239,22 +8239,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8206450410105193</v>
+        <v>0.8114013258510477</v>
       </c>
       <c r="O2">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P2">
-        <v>0.947129695925545</v>
+        <v>0.9399771496357334</v>
       </c>
       <c r="Q2">
-        <v>28.23211870828506</v>
+        <v>28.51930871185779</v>
       </c>
       <c r="R2">
         <v>-89.99999999999655</v>
       </c>
       <c r="S2">
-        <v>139.7630782572945</v>
+        <v>139.3293505030176</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -8301,22 +8301,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.7908599827081786</v>
+        <v>0.7813661795563565</v>
       </c>
       <c r="O3">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P3">
-        <v>0.9090010072409083</v>
+        <v>0.8996640132793632</v>
       </c>
       <c r="Q3">
-        <v>30.34848109574179</v>
+        <v>30.84063589229962</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S3">
-        <v>138.6605985173646</v>
+        <v>138.2191472247096</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8363,22 +8363,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.790859982736657</v>
+        <v>0.7813661795864051</v>
       </c>
       <c r="O4">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P4">
-        <v>0.9090010072437242</v>
+        <v>0.8996640132829697</v>
       </c>
       <c r="Q4">
-        <v>30.3484810962097</v>
+        <v>30.8406358927121</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S4">
-        <v>138.6605985191966</v>
+        <v>138.219147226643</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8425,22 +8425,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.790859982736657</v>
+        <v>0.781366179586405</v>
       </c>
       <c r="O5">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P5">
-        <v>0.9090010072437242</v>
+        <v>0.8996640132829697</v>
       </c>
       <c r="Q5">
-        <v>30.3484810962097</v>
+        <v>30.84063589271211</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S5">
-        <v>138.6605985191966</v>
+        <v>138.219147226643</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -8451,7 +8451,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.7260792121740363</v>
+        <v>0.7601192823969949</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -8460,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>8.384040572033424</v>
+        <v>8.777101446162604</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -8469,43 +8469,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>10.07160052780018</v>
+        <v>7.61401001298993</v>
       </c>
       <c r="I6">
-        <v>7.079996444822221</v>
+        <v>6.44697046644081</v>
       </c>
       <c r="J6">
-        <v>3.953518728204021</v>
+        <v>3.953518728204044</v>
       </c>
       <c r="K6">
-        <v>6.198216755313587</v>
+        <v>6.198216755313541</v>
       </c>
       <c r="L6">
-        <v>3.953518728224332</v>
+        <v>3.953518728224347</v>
       </c>
       <c r="M6">
-        <v>6.198216755313418</v>
+        <v>6.198216755313323</v>
       </c>
       <c r="N6">
-        <v>0.7522822461222174</v>
+        <v>0.7447096558032442</v>
       </c>
       <c r="O6">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P6">
-        <v>0.8182764246144572</v>
+        <v>0.8043344692417761</v>
       </c>
       <c r="Q6">
-        <v>36.5664944854173</v>
+        <v>37.54547206386085</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999646</v>
+        <v>-89.9999999999965</v>
       </c>
       <c r="S6">
-        <v>137.5944890480837</v>
+        <v>137.2307998938136</v>
       </c>
       <c r="T6">
-        <v>0.7260792121740361</v>
+        <v>0.7601192823969949</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -8549,22 +8549,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.7908599827461484</v>
+        <v>0.7813661795992355</v>
       </c>
       <c r="O7">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P7">
-        <v>0.9090010071773766</v>
+        <v>0.8996640132142528</v>
       </c>
       <c r="Q7">
-        <v>30.34848110150037</v>
+        <v>30.84063589828642</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S7">
-        <v>138.6605985212108</v>
+        <v>138.2191472288688</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -8611,22 +8611,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.7908599827461484</v>
+        <v>0.7813661795992355</v>
       </c>
       <c r="O8">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P8">
-        <v>0.9090010071773766</v>
+        <v>0.8996640132142528</v>
       </c>
       <c r="Q8">
-        <v>30.34848110150037</v>
+        <v>30.84063589828642</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S8">
-        <v>138.6605985212108</v>
+        <v>138.2191472288688</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -8673,22 +8673,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.7522822461707577</v>
+        <v>0.7447096558579162</v>
       </c>
       <c r="O9">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P9">
-        <v>0.8182764245447912</v>
+        <v>0.8043344691703823</v>
       </c>
       <c r="Q9">
-        <v>36.56649449154357</v>
+        <v>37.54547207015098</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999646</v>
+        <v>-89.9999999999965</v>
       </c>
       <c r="S9">
-        <v>137.5944890524971</v>
+        <v>137.2307998986324</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -8807,22 +8807,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.8206450410105193</v>
+        <v>0.8114013258510477</v>
       </c>
       <c r="O2">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P2">
-        <v>0.947129695925545</v>
+        <v>0.9399771496357334</v>
       </c>
       <c r="Q2">
-        <v>28.23211870828506</v>
+        <v>28.51930871185779</v>
       </c>
       <c r="R2">
         <v>-89.99999999999655</v>
       </c>
       <c r="S2">
-        <v>139.7630782572945</v>
+        <v>139.3293505030176</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -8869,22 +8869,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.7908599827081786</v>
+        <v>0.7813661795563565</v>
       </c>
       <c r="O3">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P3">
-        <v>0.9090010072409083</v>
+        <v>0.8996640132793632</v>
       </c>
       <c r="Q3">
-        <v>30.34848109574179</v>
+        <v>30.84063589229962</v>
       </c>
       <c r="R3">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S3">
-        <v>138.6605985173646</v>
+        <v>138.2191472247096</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -8931,22 +8931,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.790859982736657</v>
+        <v>0.7813661795864051</v>
       </c>
       <c r="O4">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P4">
-        <v>0.9090010072437242</v>
+        <v>0.8996640132829697</v>
       </c>
       <c r="Q4">
-        <v>30.3484810962097</v>
+        <v>30.8406358927121</v>
       </c>
       <c r="R4">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S4">
-        <v>138.6605985191966</v>
+        <v>138.219147226643</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -8993,22 +8993,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.790859982736657</v>
+        <v>0.781366179586405</v>
       </c>
       <c r="O5">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P5">
-        <v>0.9090010072437242</v>
+        <v>0.8996640132829697</v>
       </c>
       <c r="Q5">
-        <v>30.3484810962097</v>
+        <v>30.84063589271211</v>
       </c>
       <c r="R5">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S5">
-        <v>138.6605985191966</v>
+        <v>138.219147226643</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9019,7 +9019,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>0.7260792121740363</v>
+        <v>0.7601192823969949</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -9028,7 +9028,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>8.384040572033424</v>
+        <v>8.777101446162604</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -9037,43 +9037,43 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>10.07160052780018</v>
+        <v>7.61401001298993</v>
       </c>
       <c r="I6">
-        <v>7.079996444822221</v>
+        <v>6.44697046644081</v>
       </c>
       <c r="J6">
-        <v>3.953518728204021</v>
+        <v>3.953518728204044</v>
       </c>
       <c r="K6">
-        <v>6.198216755313587</v>
+        <v>6.198216755313541</v>
       </c>
       <c r="L6">
-        <v>3.953518728224332</v>
+        <v>3.953518728224347</v>
       </c>
       <c r="M6">
-        <v>6.198216755313418</v>
+        <v>6.198216755313323</v>
       </c>
       <c r="N6">
-        <v>0.7522822461222174</v>
+        <v>0.7447096558032442</v>
       </c>
       <c r="O6">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P6">
-        <v>0.8182764246144572</v>
+        <v>0.8043344692417761</v>
       </c>
       <c r="Q6">
-        <v>36.5664944854173</v>
+        <v>37.54547206386085</v>
       </c>
       <c r="R6">
-        <v>-89.99999999999646</v>
+        <v>-89.9999999999965</v>
       </c>
       <c r="S6">
-        <v>137.5944890480837</v>
+        <v>137.2307998938136</v>
       </c>
       <c r="T6">
-        <v>0.7260792121740361</v>
+        <v>0.7601192823969949</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -9117,22 +9117,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.7908599827461484</v>
+        <v>0.7813661795992355</v>
       </c>
       <c r="O7">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P7">
-        <v>0.9090010071773766</v>
+        <v>0.8996640132142528</v>
       </c>
       <c r="Q7">
-        <v>30.34848110150037</v>
+        <v>30.84063589828642</v>
       </c>
       <c r="R7">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S7">
-        <v>138.6605985212108</v>
+        <v>138.2191472288688</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -9179,22 +9179,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.7908599827461484</v>
+        <v>0.7813661795992355</v>
       </c>
       <c r="O8">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P8">
-        <v>0.9090010071773766</v>
+        <v>0.8996640132142528</v>
       </c>
       <c r="Q8">
-        <v>30.34848110150037</v>
+        <v>30.84063589828642</v>
       </c>
       <c r="R8">
-        <v>-89.99999999999646</v>
+        <v>-89.99999999999645</v>
       </c>
       <c r="S8">
-        <v>138.6605985212108</v>
+        <v>138.2191472288688</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -9241,22 +9241,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.7522822461707577</v>
+        <v>0.7447096558579162</v>
       </c>
       <c r="O9">
-        <v>0.9999999999994159</v>
+        <v>0.9999999999993536</v>
       </c>
       <c r="P9">
-        <v>0.8182764245447912</v>
+        <v>0.8043344691703823</v>
       </c>
       <c r="Q9">
-        <v>36.56649449154357</v>
+        <v>37.54547207015098</v>
       </c>
       <c r="R9">
-        <v>-89.99999999999646</v>
+        <v>-89.9999999999965</v>
       </c>
       <c r="S9">
-        <v>137.5944890524971</v>
+        <v>137.2307998986324</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -9375,22 +9375,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9060616641989658</v>
+        <v>0.8802988101850701</v>
       </c>
       <c r="O2">
-        <v>0.3968725684449338</v>
+        <v>0.3968725684449665</v>
       </c>
       <c r="P2">
-        <v>0.7271941441000133</v>
+        <v>0.7024566547428751</v>
       </c>
       <c r="Q2">
-        <v>4.670597650319673</v>
+        <v>4.894674322249234</v>
       </c>
       <c r="R2">
-        <v>-124.0274590209861</v>
+        <v>-124.0274590210185</v>
       </c>
       <c r="S2">
-        <v>159.4605285405378</v>
+        <v>158.8192982474765</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -9437,22 +9437,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.846264700993812</v>
+        <v>0.8167335474350077</v>
       </c>
       <c r="O3">
-        <v>0.2604212734076202</v>
+        <v>0.2604212734077005</v>
       </c>
       <c r="P3">
-        <v>0.6969936576743089</v>
+        <v>0.6673414233017352</v>
       </c>
       <c r="Q3">
-        <v>0.6639219845173334</v>
+        <v>0.9849394741810183</v>
       </c>
       <c r="R3">
-        <v>-131.9071155624327</v>
+        <v>-131.9071155624884</v>
       </c>
       <c r="S3">
-        <v>164.6924029404973</v>
+        <v>164.3721586849895</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -9499,22 +9499,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8462647009829806</v>
+        <v>0.816733547426654</v>
       </c>
       <c r="O4">
-        <v>0.2604212734213391</v>
+        <v>0.2604212734214197</v>
       </c>
       <c r="P4">
-        <v>0.6969936577098621</v>
+        <v>0.6673414233392772</v>
       </c>
       <c r="Q4">
-        <v>0.6639219873516599</v>
+        <v>0.9849394771707258</v>
       </c>
       <c r="R4">
-        <v>-131.9071155467766</v>
+        <v>-131.9071155468323</v>
       </c>
       <c r="S4">
-        <v>164.6924029399332</v>
+        <v>164.3721586845296</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -9561,22 +9561,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8462647009829806</v>
+        <v>0.8167335474266539</v>
       </c>
       <c r="O5">
-        <v>0.2604212734213392</v>
+        <v>0.2604212734214197</v>
       </c>
       <c r="P5">
-        <v>0.6969936577098621</v>
+        <v>0.6673414233392772</v>
       </c>
       <c r="Q5">
-        <v>0.6639219873516599</v>
+        <v>0.9849394771707322</v>
       </c>
       <c r="R5">
-        <v>-131.9071155467766</v>
+        <v>-131.9071155468322</v>
       </c>
       <c r="S5">
-        <v>164.6924029399332</v>
+        <v>164.3721586845296</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -9590,58 +9590,58 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>2.176343369257087</v>
+        <v>2.185725172736423</v>
       </c>
       <c r="D6">
-        <v>1.822400631222719</v>
+        <v>1.908616693875303</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>25.13024860179273</v>
+        <v>25.2385803370783</v>
       </c>
       <c r="G6">
-        <v>21.04326990015562</v>
+        <v>22.0388072397744</v>
       </c>
       <c r="H6">
-        <v>5.424025632034033</v>
+        <v>4.144030571481053</v>
       </c>
       <c r="I6">
-        <v>6.488939310918609</v>
+        <v>5.855913331295389</v>
       </c>
       <c r="J6">
-        <v>2.237816431607131</v>
+        <v>2.237816431607153</v>
       </c>
       <c r="K6">
-        <v>5.601194464564823</v>
+        <v>5.601194464564863</v>
       </c>
       <c r="L6">
-        <v>2.237816431580051</v>
+        <v>2.23781643158009</v>
       </c>
       <c r="M6">
-        <v>5.601194464517764</v>
+        <v>5.601194464517768</v>
       </c>
       <c r="N6">
-        <v>0.7090618932008848</v>
+        <v>0.6745794393373513</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.7090618931995056</v>
+        <v>0.6745794393356761</v>
       </c>
       <c r="Q6">
-        <v>-4.733513263390652</v>
+        <v>-3.987203435893121</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>175.2664867366652</v>
+        <v>176.0127965641788</v>
       </c>
       <c r="T6">
-        <v>1.676798960853586</v>
+        <v>1.880651520533738</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -9685,22 +9685,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.8462647008070597</v>
+        <v>0.8167335472536178</v>
       </c>
       <c r="O7">
-        <v>0.2604212731950655</v>
+        <v>0.2604212731951458</v>
       </c>
       <c r="P7">
-        <v>0.696993657815188</v>
+        <v>0.6673414234436642</v>
       </c>
       <c r="Q7">
-        <v>0.663921991117986</v>
+        <v>0.9849394818216273</v>
       </c>
       <c r="R7">
-        <v>-131.907115500408</v>
+        <v>-131.9071155004637</v>
       </c>
       <c r="S7">
-        <v>164.6924029492251</v>
+        <v>164.3721586951445</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -9747,22 +9747,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.8462647008070598</v>
+        <v>0.8167335472536178</v>
       </c>
       <c r="O8">
-        <v>0.2604212731950656</v>
+        <v>0.2604212731951461</v>
       </c>
       <c r="P8">
-        <v>0.696993657815188</v>
+        <v>0.6673414234436643</v>
       </c>
       <c r="Q8">
-        <v>0.6639219911179859</v>
+        <v>0.9849394818216368</v>
       </c>
       <c r="R8">
-        <v>-131.907115500408</v>
+        <v>-131.9071155004636</v>
       </c>
       <c r="S8">
-        <v>164.6924029492251</v>
+        <v>164.3721586951444</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -9809,22 +9809,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.709061892998441</v>
+        <v>0.6745794391402781</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.709061893365632</v>
+        <v>0.674579439507057</v>
       </c>
       <c r="Q9">
-        <v>-4.733513256441464</v>
+        <v>-3.987203427416789</v>
       </c>
       <c r="R9">
         <v>0</v>
       </c>
       <c r="S9">
-        <v>175.2664867430916</v>
+        <v>176.0127965716979</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -9943,22 +9943,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9060616641989659</v>
+        <v>0.8802988101850702</v>
       </c>
       <c r="O2">
-        <v>0.3968725684449342</v>
+        <v>0.3968725684449689</v>
       </c>
       <c r="P2">
-        <v>0.7271941441000128</v>
+        <v>0.7024566547428774</v>
       </c>
       <c r="Q2">
-        <v>4.670597650319693</v>
+        <v>4.894674322249227</v>
       </c>
       <c r="R2">
-        <v>-124.0274590209861</v>
+        <v>-124.0274590210181</v>
       </c>
       <c r="S2">
-        <v>159.4605285405378</v>
+        <v>158.8192982474763</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -10005,22 +10005,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8462647009938122</v>
+        <v>0.8167335474350078</v>
       </c>
       <c r="O3">
-        <v>0.2604212734076208</v>
+        <v>0.260421273407703</v>
       </c>
       <c r="P3">
-        <v>0.6969936576743084</v>
+        <v>0.6673414233017373</v>
       </c>
       <c r="Q3">
-        <v>0.6639219845173669</v>
+        <v>0.984939474181008</v>
       </c>
       <c r="R3">
-        <v>-131.9071155624327</v>
+        <v>-131.9071155624877</v>
       </c>
       <c r="S3">
-        <v>164.6924029404973</v>
+        <v>164.3721586849892</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -10067,22 +10067,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8462647009829808</v>
+        <v>0.8167335474266543</v>
       </c>
       <c r="O4">
-        <v>0.2604212734213399</v>
+        <v>0.2604212734214218</v>
       </c>
       <c r="P4">
-        <v>0.6969936577098614</v>
+        <v>0.6673414233392791</v>
       </c>
       <c r="Q4">
-        <v>0.6639219873516902</v>
+        <v>0.9849394771706896</v>
       </c>
       <c r="R4">
-        <v>-131.9071155467767</v>
+        <v>-131.9071155468317</v>
       </c>
       <c r="S4">
-        <v>164.6924029399332</v>
+        <v>164.3721586845292</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -10129,22 +10129,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8462647009829806</v>
+        <v>0.8167335474266545</v>
       </c>
       <c r="O5">
-        <v>0.2604212734213398</v>
+        <v>0.2604212734214222</v>
       </c>
       <c r="P5">
-        <v>0.6969936577098614</v>
+        <v>0.6673414233392788</v>
       </c>
       <c r="Q5">
-        <v>0.6639219873516896</v>
+        <v>0.984939477170704</v>
       </c>
       <c r="R5">
-        <v>-131.9071155467767</v>
+        <v>-131.9071155468317</v>
       </c>
       <c r="S5">
-        <v>164.6924029399332</v>
+        <v>164.3721586845292</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -10158,58 +10158,58 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>2.176343369257083</v>
+        <v>2.185725172736424</v>
       </c>
       <c r="D6">
-        <v>1.822400631222718</v>
+        <v>1.908616693875294</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>25.13024860179268</v>
+        <v>25.23858033707831</v>
       </c>
       <c r="G6">
-        <v>21.0432699001556</v>
+        <v>22.03880723977429</v>
       </c>
       <c r="H6">
-        <v>5.424025632034074</v>
+        <v>4.144030571481082</v>
       </c>
       <c r="I6">
-        <v>6.488939310918615</v>
+        <v>5.855913331295391</v>
       </c>
       <c r="J6">
-        <v>2.237816431607153</v>
+        <v>2.237816431607152</v>
       </c>
       <c r="K6">
-        <v>5.601194464564824</v>
+        <v>5.601194464564855</v>
       </c>
       <c r="L6">
-        <v>2.237816431580073</v>
+        <v>2.237816431580077</v>
       </c>
       <c r="M6">
-        <v>5.601194464517769</v>
+        <v>5.60119446451777</v>
       </c>
       <c r="N6">
-        <v>0.7090618932008852</v>
+        <v>0.6745794393373513</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.7090618931995054</v>
+        <v>0.6745794393356759</v>
       </c>
       <c r="Q6">
-        <v>-4.733513263390649</v>
+        <v>-3.987203435893149</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>175.2664867366652</v>
+        <v>176.0127965641784</v>
       </c>
       <c r="T6">
-        <v>1.676798960853571</v>
+        <v>1.880651520533746</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -10253,22 +10253,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.846264700798683</v>
+        <v>0.8167335472453784</v>
       </c>
       <c r="O7">
-        <v>0.2604212731842913</v>
+        <v>0.2604212731843733</v>
       </c>
       <c r="P7">
-        <v>0.6969936578202027</v>
+        <v>0.6673414234486367</v>
       </c>
       <c r="Q7">
-        <v>0.6639219912973687</v>
+        <v>0.9849394820430781</v>
       </c>
       <c r="R7">
-        <v>-131.9071154982001</v>
+        <v>-131.907115498255</v>
       </c>
       <c r="S7">
-        <v>164.6924029496676</v>
+        <v>164.3721586956496</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -10315,22 +10315,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.8462647007986829</v>
+        <v>0.8167335472453786</v>
       </c>
       <c r="O8">
-        <v>0.2604212731842914</v>
+        <v>0.2604212731843736</v>
       </c>
       <c r="P8">
-        <v>0.6969936578202029</v>
+        <v>0.6673414234486366</v>
       </c>
       <c r="Q8">
-        <v>0.6639219912973759</v>
+        <v>0.9849394820430861</v>
       </c>
       <c r="R8">
-        <v>-131.9071154982001</v>
+        <v>-131.9071154982551</v>
       </c>
       <c r="S8">
-        <v>164.6924029496676</v>
+        <v>164.3721586956496</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -10377,22 +10377,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.7090618929888015</v>
+        <v>0.6745794391308935</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.7090618933735422</v>
+        <v>0.6745794395152179</v>
       </c>
       <c r="Q9">
-        <v>-4.733513256110531</v>
+        <v>-3.987203427013194</v>
       </c>
       <c r="R9">
         <v>0</v>
       </c>
       <c r="S9">
-        <v>175.2664867433976</v>
+        <v>176.0127965720555</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -10511,22 +10511,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.018870157837147</v>
+        <v>1.012333429039879</v>
       </c>
       <c r="O2">
-        <v>0.789904846197363</v>
+        <v>0.7899048461973291</v>
       </c>
       <c r="P2">
-        <v>0.8974666059493107</v>
+        <v>0.8922470519588949</v>
       </c>
       <c r="Q2">
-        <v>18.93851635663321</v>
+        <v>19.00454113733399</v>
       </c>
       <c r="R2">
-        <v>-103.2140010815882</v>
+        <v>-103.2140010815902</v>
       </c>
       <c r="S2">
-        <v>150.765245248015</v>
+        <v>150.5023805559353</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -10573,22 +10573,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9883550265396278</v>
+        <v>0.9809444270614998</v>
       </c>
       <c r="O3">
-        <v>0.7229340275226227</v>
+        <v>0.7229340275225912</v>
       </c>
       <c r="P3">
-        <v>0.8699180559166261</v>
+        <v>0.8634039464346522</v>
       </c>
       <c r="Q3">
-        <v>17.52889632178974</v>
+        <v>17.63611645241662</v>
       </c>
       <c r="R3">
-        <v>-103.7857893953951</v>
+        <v>-103.7857893953976</v>
       </c>
       <c r="S3">
-        <v>152.2959209918941</v>
+        <v>152.0324806142833</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -10635,22 +10635,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9883550265373902</v>
+        <v>0.9809444270598852</v>
       </c>
       <c r="O4">
-        <v>0.7229340275378111</v>
+        <v>0.7229340275377795</v>
       </c>
       <c r="P4">
-        <v>0.8699180559342961</v>
+        <v>0.8634039464526181</v>
       </c>
       <c r="Q4">
-        <v>17.52889632293214</v>
+        <v>17.63611645357535</v>
       </c>
       <c r="R4">
-        <v>-103.7857893929796</v>
+        <v>-103.7857893929821</v>
       </c>
       <c r="S4">
-        <v>152.2959209922153</v>
+        <v>152.0324806146461</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -10697,22 +10697,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9883550265373903</v>
+        <v>0.9809444270598848</v>
       </c>
       <c r="O5">
-        <v>0.7229340275378111</v>
+        <v>0.7229340275377794</v>
       </c>
       <c r="P5">
-        <v>0.8699180559342962</v>
+        <v>0.8634039464526182</v>
       </c>
       <c r="Q5">
-        <v>17.52889632293214</v>
+        <v>17.63611645357535</v>
       </c>
       <c r="R5">
-        <v>-103.7857893929796</v>
+        <v>-103.7857893929821</v>
       </c>
       <c r="S5">
-        <v>152.2959209922153</v>
+        <v>152.0324806146461</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -10726,58 +10726,58 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.9981927965818105</v>
+        <v>1.001759587253732</v>
       </c>
       <c r="D6">
-        <v>0.9225804714925246</v>
+        <v>0.945156822242371</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>11.52613759619307</v>
+        <v>11.56732334728462</v>
       </c>
       <c r="G6">
-        <v>10.65304167130602</v>
+        <v>10.91373091496088</v>
       </c>
       <c r="H6">
-        <v>5.424025632034033</v>
+        <v>4.144030571481053</v>
       </c>
       <c r="I6">
-        <v>6.488939310918609</v>
+        <v>5.855913331295389</v>
       </c>
       <c r="J6">
-        <v>2.237816431607131</v>
+        <v>2.237816431607153</v>
       </c>
       <c r="K6">
-        <v>5.601194464564823</v>
+        <v>5.601194464564863</v>
       </c>
       <c r="L6">
-        <v>2.237816431580051</v>
+        <v>2.23781643158009</v>
       </c>
       <c r="M6">
-        <v>5.601194464517764</v>
+        <v>5.601194464517768</v>
       </c>
       <c r="N6">
-        <v>0.9205894029394273</v>
+        <v>0.9122451454600227</v>
       </c>
       <c r="O6">
-        <v>0.6059501515843788</v>
+        <v>0.6059501515843446</v>
       </c>
       <c r="P6">
-        <v>0.8427568787084933</v>
+        <v>0.8340298058017078</v>
       </c>
       <c r="Q6">
-        <v>16.20299603543411</v>
+        <v>16.43051994443773</v>
       </c>
       <c r="R6">
-        <v>-100.6772421604384</v>
+        <v>-100.677242160442</v>
       </c>
       <c r="S6">
-        <v>156.3124525110437</v>
+        <v>156.13545329578</v>
       </c>
       <c r="T6">
-        <v>0.8704495857947017</v>
+        <v>0.9253554392383685</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -10821,22 +10821,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.988355026461057</v>
+        <v>0.9809444269844851</v>
       </c>
       <c r="O7">
-        <v>0.7229340274619844</v>
+        <v>0.7229340274619531</v>
       </c>
       <c r="P7">
-        <v>0.8699180559566704</v>
+        <v>0.8634039464735319</v>
       </c>
       <c r="Q7">
-        <v>17.52889632504997</v>
+        <v>17.6361164558582</v>
       </c>
       <c r="R7">
-        <v>-103.7857893831563</v>
+        <v>-103.7857893831588</v>
       </c>
       <c r="S7">
-        <v>152.2959209971516</v>
+        <v>152.0324806197792</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -10883,22 +10883,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.988355026461057</v>
+        <v>0.9809444269844851</v>
       </c>
       <c r="O8">
-        <v>0.7229340274619847</v>
+        <v>0.7229340274619529</v>
       </c>
       <c r="P8">
-        <v>0.8699180559566704</v>
+        <v>0.863403946473532</v>
       </c>
       <c r="Q8">
-        <v>17.52889632504997</v>
+        <v>17.63611645585819</v>
       </c>
       <c r="R8">
-        <v>-103.7857893831563</v>
+        <v>-103.7857893831588</v>
       </c>
       <c r="S8">
-        <v>152.2959209971516</v>
+        <v>152.0324806197792</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -10945,22 +10945,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9205894028569055</v>
+        <v>0.9122451453792305</v>
       </c>
       <c r="O9">
-        <v>0.6059501515323414</v>
+        <v>0.6059501515323074</v>
       </c>
       <c r="P9">
-        <v>0.8427568787572179</v>
+        <v>0.8340298058496107</v>
       </c>
       <c r="Q9">
-        <v>16.20299603904581</v>
+        <v>16.43051994826991</v>
       </c>
       <c r="R9">
-        <v>-100.6772421448166</v>
+        <v>-100.6772421448202</v>
       </c>
       <c r="S9">
-        <v>156.3124525164484</v>
+        <v>156.1354533014574</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -11079,22 +11079,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.018870157837147</v>
+        <v>1.012333429039879</v>
       </c>
       <c r="O2">
-        <v>0.7899048461973638</v>
+        <v>0.7899048461973303</v>
       </c>
       <c r="P2">
-        <v>0.8974666059493105</v>
+        <v>0.8922470519588958</v>
       </c>
       <c r="Q2">
-        <v>18.93851635663323</v>
+        <v>19.00454113733399</v>
       </c>
       <c r="R2">
-        <v>-103.2140010815882</v>
+        <v>-103.2140010815901</v>
       </c>
       <c r="S2">
-        <v>150.765245248015</v>
+        <v>150.5023805559352</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -11141,22 +11141,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9883550265396278</v>
+        <v>0.9809444270615</v>
       </c>
       <c r="O3">
-        <v>0.7229340275226236</v>
+        <v>0.7229340275225921</v>
       </c>
       <c r="P3">
-        <v>0.8699180559166259</v>
+        <v>0.8634039464346531</v>
       </c>
       <c r="Q3">
-        <v>17.52889632178977</v>
+        <v>17.63611645241662</v>
       </c>
       <c r="R3">
-        <v>-103.7857893953951</v>
+        <v>-103.7857893953976</v>
       </c>
       <c r="S3">
-        <v>152.295920991894</v>
+        <v>152.0324806142833</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -11203,22 +11203,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9883550265373899</v>
+        <v>0.9809444270598852</v>
       </c>
       <c r="O4">
-        <v>0.7229340275378119</v>
+        <v>0.7229340275377806</v>
       </c>
       <c r="P4">
-        <v>0.8699180559342956</v>
+        <v>0.863403946452619</v>
       </c>
       <c r="Q4">
-        <v>17.52889632293217</v>
+        <v>17.63611645357535</v>
       </c>
       <c r="R4">
-        <v>-103.7857893929796</v>
+        <v>-103.785789392982</v>
       </c>
       <c r="S4">
-        <v>152.2959209922153</v>
+        <v>152.0324806146461</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -11265,22 +11265,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9883550265373899</v>
+        <v>0.9809444270598852</v>
       </c>
       <c r="O5">
-        <v>0.722934027537812</v>
+        <v>0.7229340275377806</v>
       </c>
       <c r="P5">
-        <v>0.8699180559342958</v>
+        <v>0.8634039464526189</v>
       </c>
       <c r="Q5">
-        <v>17.52889632293217</v>
+        <v>17.63611645357535</v>
       </c>
       <c r="R5">
-        <v>-103.7857893929796</v>
+        <v>-103.785789392982</v>
       </c>
       <c r="S5">
-        <v>152.2959209922153</v>
+        <v>152.0324806146461</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -11294,58 +11294,58 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.9981927965818093</v>
+        <v>1.001759587253733</v>
       </c>
       <c r="D6">
-        <v>0.9225804714925244</v>
+        <v>0.9451568222423685</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>11.52613759619306</v>
+        <v>11.56732334728462</v>
       </c>
       <c r="G6">
-        <v>10.65304167130602</v>
+        <v>10.91373091496085</v>
       </c>
       <c r="H6">
-        <v>5.424025632034074</v>
+        <v>4.144030571481082</v>
       </c>
       <c r="I6">
-        <v>6.488939310918615</v>
+        <v>5.855913331295391</v>
       </c>
       <c r="J6">
-        <v>2.237816431607153</v>
+        <v>2.237816431607152</v>
       </c>
       <c r="K6">
-        <v>5.601194464564824</v>
+        <v>5.601194464564855</v>
       </c>
       <c r="L6">
-        <v>2.237816431580073</v>
+        <v>2.237816431580077</v>
       </c>
       <c r="M6">
-        <v>5.601194464517769</v>
+        <v>5.60119446451777</v>
       </c>
       <c r="N6">
-        <v>0.920589402939427</v>
+        <v>0.9122451454600227</v>
       </c>
       <c r="O6">
-        <v>0.6059501515843795</v>
+        <v>0.605950151584346</v>
       </c>
       <c r="P6">
-        <v>0.8427568787084929</v>
+        <v>0.8340298058017085</v>
       </c>
       <c r="Q6">
-        <v>16.20299603543414</v>
+        <v>16.43051994443773</v>
       </c>
       <c r="R6">
-        <v>-100.6772421604384</v>
+        <v>-100.6772421604419</v>
       </c>
       <c r="S6">
-        <v>156.3124525110437</v>
+        <v>156.13545329578</v>
       </c>
       <c r="T6">
-        <v>0.870449585794698</v>
+        <v>0.92535543923837</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -11389,22 +11389,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9883550264574218</v>
+        <v>0.9809444269808948</v>
       </c>
       <c r="O7">
-        <v>0.7229340274583745</v>
+        <v>0.7229340274583432</v>
       </c>
       <c r="P7">
-        <v>0.8699180559577353</v>
+        <v>0.8634039464745286</v>
       </c>
       <c r="Q7">
-        <v>17.52889632515084</v>
+        <v>17.6361164559669</v>
       </c>
       <c r="R7">
-        <v>-103.7857893826886</v>
+        <v>-103.785789382691</v>
       </c>
       <c r="S7">
-        <v>152.2959209973866</v>
+        <v>152.0324806200236</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -11451,22 +11451,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9883550264574218</v>
+        <v>0.9809444269808949</v>
       </c>
       <c r="O8">
-        <v>0.7229340274583747</v>
+        <v>0.7229340274583435</v>
       </c>
       <c r="P8">
-        <v>0.8699180559577353</v>
+        <v>0.8634039464745283</v>
       </c>
       <c r="Q8">
-        <v>17.52889632515085</v>
+        <v>17.6361164559669</v>
       </c>
       <c r="R8">
-        <v>-103.7857893826885</v>
+        <v>-103.785789382691</v>
       </c>
       <c r="S8">
-        <v>152.2959209973866</v>
+        <v>152.0324806200236</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -11513,22 +11513,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9205894028529759</v>
+        <v>0.9122451453753833</v>
       </c>
       <c r="O9">
-        <v>0.6059501515298644</v>
+        <v>0.6059501515298307</v>
       </c>
       <c r="P9">
-        <v>0.8427568787595375</v>
+        <v>0.8340298058518926</v>
       </c>
       <c r="Q9">
-        <v>16.20299603921782</v>
+        <v>16.43051994845239</v>
       </c>
       <c r="R9">
-        <v>-100.6772421440727</v>
+        <v>-100.6772421440763</v>
       </c>
       <c r="S9">
-        <v>156.3124525167057</v>
+        <v>156.1354533017277</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -11647,22 +11647,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9264026591110941</v>
+        <v>0.9008805616346987</v>
       </c>
       <c r="O2">
-        <v>0.4986603516025517</v>
+        <v>0.4986603516026912</v>
       </c>
       <c r="P2">
-        <v>0.6799263258459319</v>
+        <v>0.6601514092604912</v>
       </c>
       <c r="Q2">
-        <v>6.259570784359546</v>
+        <v>6.04827156918943</v>
       </c>
       <c r="R2">
-        <v>-127.9801517751898</v>
+        <v>-127.9801517751726</v>
       </c>
       <c r="S2">
-        <v>154.5623657971338</v>
+        <v>153.1527191485391</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -11709,22 +11709,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8545773200093233</v>
+        <v>0.8249241208093135</v>
       </c>
       <c r="O3">
-        <v>0.3451994260363932</v>
+        <v>0.3451994260365135</v>
       </c>
       <c r="P3">
-        <v>0.6550597341008624</v>
+        <v>0.6279892374998582</v>
       </c>
       <c r="Q3">
-        <v>2.412928811293926</v>
+        <v>2.343640655781063</v>
       </c>
       <c r="R3">
-        <v>-133.0240089402593</v>
+        <v>-133.0240089402312</v>
       </c>
       <c r="S3">
-        <v>160.7112239499163</v>
+        <v>159.6261613779621</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -11771,22 +11771,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8545773199974886</v>
+        <v>0.824924120801374</v>
       </c>
       <c r="O4">
-        <v>0.3451994260647946</v>
+        <v>0.345199426064915</v>
       </c>
       <c r="P4">
-        <v>0.6550597341516032</v>
+        <v>0.6279892375540608</v>
       </c>
       <c r="Q4">
-        <v>2.412928815564774</v>
+        <v>2.343640660285857</v>
       </c>
       <c r="R4">
-        <v>-133.0240089227219</v>
+        <v>-133.0240089226938</v>
       </c>
       <c r="S4">
-        <v>160.7112239487163</v>
+        <v>159.626161377037</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -11833,22 +11833,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8545773199974888</v>
+        <v>0.824924120801374</v>
       </c>
       <c r="O5">
-        <v>0.3451994260647945</v>
+        <v>0.3451994260649149</v>
       </c>
       <c r="P5">
-        <v>0.6550597341516032</v>
+        <v>0.6279892375540608</v>
       </c>
       <c r="Q5">
-        <v>2.412928815564767</v>
+        <v>2.343640660285842</v>
       </c>
       <c r="R5">
-        <v>-133.0240089227219</v>
+        <v>-133.0240089226939</v>
       </c>
       <c r="S5">
-        <v>160.7112239487163</v>
+        <v>159.626161377037</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -11862,58 +11862,58 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>1.610978819204034</v>
+        <v>1.62470070764501</v>
       </c>
       <c r="D6">
-        <v>1.306941916567834</v>
+        <v>1.371103885022675</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>18.60198109852469</v>
+        <v>18.76042781822844</v>
       </c>
       <c r="G6">
-        <v>15.09126534691289</v>
+        <v>15.83214394209566</v>
       </c>
       <c r="H6">
-        <v>10.07160052779999</v>
+        <v>7.614010012989719</v>
       </c>
       <c r="I6">
-        <v>7.079996444822623</v>
+        <v>6.446970466441317</v>
       </c>
       <c r="J6">
-        <v>3.953518728206193</v>
+        <v>3.953518728206214</v>
       </c>
       <c r="K6">
-        <v>6.198216755282932</v>
+        <v>6.198216755282955</v>
       </c>
       <c r="L6">
-        <v>3.953518728223953</v>
+        <v>3.953518728224016</v>
       </c>
       <c r="M6">
-        <v>6.19821675531351</v>
+        <v>6.198216755313494</v>
       </c>
       <c r="N6">
-        <v>0.6759626201272257</v>
+        <v>0.6385065885177484</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.6759626201265756</v>
+        <v>0.6385065885171644</v>
       </c>
       <c r="Q6">
-        <v>-5.086999826385493</v>
+        <v>-4.610782588584486</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>174.913000173459</v>
+        <v>175.3892174112333</v>
       </c>
       <c r="T6">
-        <v>1.098134111521839</v>
+        <v>1.279982489867891</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -11957,22 +11957,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.8545773198364129</v>
+        <v>0.8249241206409469</v>
       </c>
       <c r="O7">
-        <v>0.3451994258394096</v>
+        <v>0.3451994258395302</v>
       </c>
       <c r="P7">
-        <v>0.6550597342282262</v>
+        <v>0.6279892376252257</v>
       </c>
       <c r="Q7">
-        <v>2.412928817402775</v>
+        <v>2.343640662900258</v>
       </c>
       <c r="R7">
-        <v>-133.0240088963045</v>
+        <v>-133.0240088962763</v>
       </c>
       <c r="S7">
-        <v>160.7112239581772</v>
+        <v>159.6261613879374</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -12019,22 +12019,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.8545773198364129</v>
+        <v>0.8249241206409471</v>
       </c>
       <c r="O8">
-        <v>0.3451994258394098</v>
+        <v>0.34519942583953</v>
       </c>
       <c r="P8">
-        <v>0.6550597342282262</v>
+        <v>0.6279892376252261</v>
       </c>
       <c r="Q8">
-        <v>2.412928817402777</v>
+        <v>2.343640662900241</v>
       </c>
       <c r="R8">
-        <v>-133.0240088963044</v>
+        <v>-133.0240088962763</v>
       </c>
       <c r="S8">
-        <v>160.7112239581772</v>
+        <v>159.6261613879374</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -12081,22 +12081,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.6759626199309131</v>
+        <v>0.6385065883253104</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.67596262028224</v>
+        <v>0.638506588676658</v>
       </c>
       <c r="Q9">
-        <v>-5.086999820445542</v>
+        <v>-4.610782580991188</v>
       </c>
       <c r="R9">
         <v>0</v>
       </c>
       <c r="S9">
-        <v>174.9130001790594</v>
+        <v>175.3892174182046</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -12432,22 +12432,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9264026591110941</v>
+        <v>0.9008805616346987</v>
       </c>
       <c r="O2">
-        <v>0.4986603516025517</v>
+        <v>0.4986603516026912</v>
       </c>
       <c r="P2">
-        <v>0.6799263258459319</v>
+        <v>0.6601514092604912</v>
       </c>
       <c r="Q2">
-        <v>6.259570784359546</v>
+        <v>6.04827156918943</v>
       </c>
       <c r="R2">
-        <v>-127.9801517751898</v>
+        <v>-127.9801517751726</v>
       </c>
       <c r="S2">
-        <v>154.5623657971338</v>
+        <v>153.1527191485391</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -12494,22 +12494,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.8545773200093233</v>
+        <v>0.8249241208093135</v>
       </c>
       <c r="O3">
-        <v>0.3451994260363932</v>
+        <v>0.3451994260365135</v>
       </c>
       <c r="P3">
-        <v>0.6550597341008624</v>
+        <v>0.6279892374998582</v>
       </c>
       <c r="Q3">
-        <v>2.412928811293926</v>
+        <v>2.343640655781063</v>
       </c>
       <c r="R3">
-        <v>-133.0240089402593</v>
+        <v>-133.0240089402312</v>
       </c>
       <c r="S3">
-        <v>160.7112239499163</v>
+        <v>159.6261613779621</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -12556,22 +12556,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.8545773199974886</v>
+        <v>0.824924120801374</v>
       </c>
       <c r="O4">
-        <v>0.3451994260647946</v>
+        <v>0.345199426064915</v>
       </c>
       <c r="P4">
-        <v>0.6550597341516032</v>
+        <v>0.6279892375540608</v>
       </c>
       <c r="Q4">
-        <v>2.412928815564774</v>
+        <v>2.343640660285857</v>
       </c>
       <c r="R4">
-        <v>-133.0240089227219</v>
+        <v>-133.0240089226938</v>
       </c>
       <c r="S4">
-        <v>160.7112239487163</v>
+        <v>159.626161377037</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -12618,22 +12618,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.8545773199974888</v>
+        <v>0.824924120801374</v>
       </c>
       <c r="O5">
-        <v>0.3451994260647945</v>
+        <v>0.3451994260649149</v>
       </c>
       <c r="P5">
-        <v>0.6550597341516032</v>
+        <v>0.6279892375540608</v>
       </c>
       <c r="Q5">
-        <v>2.412928815564767</v>
+        <v>2.343640660285842</v>
       </c>
       <c r="R5">
-        <v>-133.0240089227219</v>
+        <v>-133.0240089226939</v>
       </c>
       <c r="S5">
-        <v>160.7112239487163</v>
+        <v>159.626161377037</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -12647,58 +12647,58 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>1.610978819204034</v>
+        <v>1.62470070764501</v>
       </c>
       <c r="D6">
-        <v>1.306941916567834</v>
+        <v>1.371103885022675</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>18.60198109852469</v>
+        <v>18.76042781822844</v>
       </c>
       <c r="G6">
-        <v>15.09126534691289</v>
+        <v>15.83214394209566</v>
       </c>
       <c r="H6">
-        <v>10.07160052779999</v>
+        <v>7.614010012989719</v>
       </c>
       <c r="I6">
-        <v>7.079996444822623</v>
+        <v>6.446970466441317</v>
       </c>
       <c r="J6">
-        <v>3.953518728206193</v>
+        <v>3.953518728206214</v>
       </c>
       <c r="K6">
-        <v>6.198216755282932</v>
+        <v>6.198216755282955</v>
       </c>
       <c r="L6">
-        <v>3.953518728223953</v>
+        <v>3.953518728224016</v>
       </c>
       <c r="M6">
-        <v>6.19821675531351</v>
+        <v>6.198216755313494</v>
       </c>
       <c r="N6">
-        <v>0.6759626201272257</v>
+        <v>0.6385065885177484</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.6759626201265756</v>
+        <v>0.6385065885171644</v>
       </c>
       <c r="Q6">
-        <v>-5.086999826385493</v>
+        <v>-4.610782588584486</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>174.913000173459</v>
+        <v>175.3892174112333</v>
       </c>
       <c r="T6">
-        <v>1.098134111521839</v>
+        <v>1.279982489867891</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -12742,22 +12742,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.8545773198364129</v>
+        <v>0.8249241206409469</v>
       </c>
       <c r="O7">
-        <v>0.3451994258394096</v>
+        <v>0.3451994258395302</v>
       </c>
       <c r="P7">
-        <v>0.6550597342282262</v>
+        <v>0.6279892376252257</v>
       </c>
       <c r="Q7">
-        <v>2.412928817402775</v>
+        <v>2.343640662900258</v>
       </c>
       <c r="R7">
-        <v>-133.0240088963045</v>
+        <v>-133.0240088962763</v>
       </c>
       <c r="S7">
-        <v>160.7112239581772</v>
+        <v>159.6261613879374</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -12804,22 +12804,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.8545773198364129</v>
+        <v>0.8249241206409471</v>
       </c>
       <c r="O8">
-        <v>0.3451994258394098</v>
+        <v>0.34519942583953</v>
       </c>
       <c r="P8">
-        <v>0.6550597342282262</v>
+        <v>0.6279892376252261</v>
       </c>
       <c r="Q8">
-        <v>2.412928817402777</v>
+        <v>2.343640662900241</v>
       </c>
       <c r="R8">
-        <v>-133.0240088963044</v>
+        <v>-133.0240088962763</v>
       </c>
       <c r="S8">
-        <v>160.7112239581772</v>
+        <v>159.6261613879374</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -12866,22 +12866,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.6759626199309131</v>
+        <v>0.6385065883253104</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.67596262028224</v>
+        <v>0.638506588676658</v>
       </c>
       <c r="Q9">
-        <v>-5.086999820445542</v>
+        <v>-4.610782580991188</v>
       </c>
       <c r="R9">
         <v>0</v>
       </c>
       <c r="S9">
-        <v>174.9130001790594</v>
+        <v>175.3892174182046</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -13000,22 +13000,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9481529538720906</v>
+        <v>0.9395756489355315</v>
       </c>
       <c r="O2">
-        <v>0.7322760567500223</v>
+        <v>0.7322760567500914</v>
       </c>
       <c r="P2">
-        <v>0.8195702772728284</v>
+        <v>0.8131326300099634</v>
       </c>
       <c r="Q2">
-        <v>18.35097919590552</v>
+        <v>18.41212906161127</v>
       </c>
       <c r="R2">
-        <v>-105.0054683023685</v>
+        <v>-105.0054683023667</v>
       </c>
       <c r="S2">
-        <v>150.0800940821339</v>
+        <v>149.6760428132002</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -13062,22 +13062,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9063792353652225</v>
+        <v>0.8967513407179986</v>
       </c>
       <c r="O3">
-        <v>0.6518511244466934</v>
+        <v>0.6518511244467626</v>
       </c>
       <c r="P3">
-        <v>0.7957851127118389</v>
+        <v>0.7871653857144373</v>
       </c>
       <c r="Q3">
-        <v>16.96787656333692</v>
+        <v>17.12839440493406</v>
       </c>
       <c r="R3">
-        <v>-104.2907188442087</v>
+        <v>-104.2907188442066</v>
       </c>
       <c r="S3">
-        <v>152.5232317989533</v>
+        <v>152.1628946801794</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -13124,22 +13124,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9063792353665444</v>
+        <v>0.8967513407208019</v>
       </c>
       <c r="O4">
-        <v>0.6518511244809749</v>
+        <v>0.6518511244810444</v>
       </c>
       <c r="P4">
-        <v>0.7957851127408442</v>
+        <v>0.7871653857444234</v>
       </c>
       <c r="Q4">
-        <v>16.96787656541303</v>
+        <v>17.12839440703172</v>
       </c>
       <c r="R4">
-        <v>-104.2907188403053</v>
+        <v>-104.2907188403032</v>
       </c>
       <c r="S4">
-        <v>152.5232317990344</v>
+        <v>152.1628946803457</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -13186,22 +13186,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9063792353665444</v>
+        <v>0.8967513407208019</v>
       </c>
       <c r="O5">
-        <v>0.6518511244809749</v>
+        <v>0.6518511244810443</v>
       </c>
       <c r="P5">
-        <v>0.7957851127408442</v>
+        <v>0.7871653857444234</v>
       </c>
       <c r="Q5">
-        <v>16.96787656541303</v>
+        <v>17.12839440703171</v>
       </c>
       <c r="R5">
-        <v>-104.2907188403053</v>
+        <v>-104.2907188403031</v>
       </c>
       <c r="S5">
-        <v>152.5232317990344</v>
+        <v>152.1628946803457</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -13215,58 +13215,58 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.8172794759706623</v>
+        <v>0.8192909477601665</v>
       </c>
       <c r="D6">
-        <v>0.7217366689642835</v>
+        <v>0.7477476736924514</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>9.437130509096363</v>
+        <v>9.460356984679116</v>
       </c>
       <c r="G6">
-        <v>8.333897202211057</v>
+        <v>8.634246413845066</v>
       </c>
       <c r="H6">
-        <v>10.07160052779999</v>
+        <v>7.614010012989719</v>
       </c>
       <c r="I6">
-        <v>7.079996444822623</v>
+        <v>6.446970466441317</v>
       </c>
       <c r="J6">
-        <v>3.953518728206193</v>
+        <v>3.953518728206214</v>
       </c>
       <c r="K6">
-        <v>6.198216755282932</v>
+        <v>6.198216755282955</v>
       </c>
       <c r="L6">
-        <v>3.953518728223953</v>
+        <v>3.953518728224016</v>
       </c>
       <c r="M6">
-        <v>6.19821675531351</v>
+        <v>6.198216755313494</v>
       </c>
       <c r="N6">
-        <v>0.8055518480312192</v>
+        <v>0.7946343373671535</v>
       </c>
       <c r="O6">
-        <v>0.4931849650005627</v>
+        <v>0.4931849650006355</v>
       </c>
       <c r="P6">
-        <v>0.7735594206637819</v>
+        <v>0.7609282792460932</v>
       </c>
       <c r="Q6">
-        <v>15.34097325496876</v>
+        <v>15.80538487780017</v>
       </c>
       <c r="R6">
-        <v>-96.35596491160986</v>
+        <v>-96.35596491160764</v>
       </c>
       <c r="S6">
-        <v>159.014630398495</v>
+        <v>158.917217550757</v>
       </c>
       <c r="T6">
-        <v>0.6571513103758266</v>
+        <v>0.717549443297119</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -13310,22 +13310,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9063792352899561</v>
+        <v>0.8967513406455309</v>
       </c>
       <c r="O7">
-        <v>0.6518511244056876</v>
+        <v>0.651851124405757</v>
       </c>
       <c r="P7">
-        <v>0.7957851127634173</v>
+        <v>0.7871653857651081</v>
       </c>
       <c r="Q7">
-        <v>16.96787656741729</v>
+        <v>17.12839440928086</v>
       </c>
       <c r="R7">
-        <v>-104.2907188297765</v>
+        <v>-104.2907188297744</v>
       </c>
       <c r="S7">
-        <v>152.523231804048</v>
+        <v>152.1628946856566</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -13372,22 +13372,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9063792352899561</v>
+        <v>0.8967513406455307</v>
       </c>
       <c r="O8">
-        <v>0.6518511244056876</v>
+        <v>0.651851124405757</v>
       </c>
       <c r="P8">
-        <v>0.7957851127634173</v>
+        <v>0.7871653857651082</v>
       </c>
       <c r="Q8">
-        <v>16.9678765674173</v>
+        <v>17.12839440928086</v>
       </c>
       <c r="R8">
-        <v>-104.2907188297765</v>
+        <v>-104.2907188297744</v>
       </c>
       <c r="S8">
-        <v>152.523231804048</v>
+        <v>152.1628946856566</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -13434,22 +13434,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8055518479482852</v>
+        <v>0.7946343372874243</v>
       </c>
       <c r="O9">
-        <v>0.4931849649794133</v>
+        <v>0.4931849649794861</v>
       </c>
       <c r="P9">
-        <v>0.773559420726195</v>
+        <v>0.760928279308372</v>
       </c>
       <c r="Q9">
-        <v>15.34097325963534</v>
+        <v>15.80538488283764</v>
       </c>
       <c r="R9">
-        <v>-96.35596489078564</v>
+        <v>-96.35596489078344</v>
       </c>
       <c r="S9">
-        <v>159.0146304036402</v>
+        <v>158.9172175563322</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -13568,22 +13568,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>0.9481529538720906</v>
+        <v>0.9395756489355315</v>
       </c>
       <c r="O2">
-        <v>0.7322760567500223</v>
+        <v>0.7322760567500914</v>
       </c>
       <c r="P2">
-        <v>0.8195702772728284</v>
+        <v>0.8131326300099634</v>
       </c>
       <c r="Q2">
-        <v>18.35097919590552</v>
+        <v>18.41212906161127</v>
       </c>
       <c r="R2">
-        <v>-105.0054683023685</v>
+        <v>-105.0054683023667</v>
       </c>
       <c r="S2">
-        <v>150.0800940821339</v>
+        <v>149.6760428132002</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -13630,22 +13630,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>0.9063792353652225</v>
+        <v>0.8967513407179986</v>
       </c>
       <c r="O3">
-        <v>0.6518511244466934</v>
+        <v>0.6518511244467626</v>
       </c>
       <c r="P3">
-        <v>0.7957851127118389</v>
+        <v>0.7871653857144373</v>
       </c>
       <c r="Q3">
-        <v>16.96787656333692</v>
+        <v>17.12839440493406</v>
       </c>
       <c r="R3">
-        <v>-104.2907188442087</v>
+        <v>-104.2907188442066</v>
       </c>
       <c r="S3">
-        <v>152.5232317989533</v>
+        <v>152.1628946801794</v>
       </c>
       <c r="T3">
         <v>0</v>
@@ -13692,22 +13692,22 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>0.9063792353665444</v>
+        <v>0.8967513407208019</v>
       </c>
       <c r="O4">
-        <v>0.6518511244809749</v>
+        <v>0.6518511244810444</v>
       </c>
       <c r="P4">
-        <v>0.7957851127408442</v>
+        <v>0.7871653857444234</v>
       </c>
       <c r="Q4">
-        <v>16.96787656541303</v>
+        <v>17.12839440703172</v>
       </c>
       <c r="R4">
-        <v>-104.2907188403053</v>
+        <v>-104.2907188403032</v>
       </c>
       <c r="S4">
-        <v>152.5232317990344</v>
+        <v>152.1628946803457</v>
       </c>
       <c r="T4">
         <v>0</v>
@@ -13754,22 +13754,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.9063792353665444</v>
+        <v>0.8967513407208019</v>
       </c>
       <c r="O5">
-        <v>0.6518511244809749</v>
+        <v>0.6518511244810443</v>
       </c>
       <c r="P5">
-        <v>0.7957851127408442</v>
+        <v>0.7871653857444234</v>
       </c>
       <c r="Q5">
-        <v>16.96787656541303</v>
+        <v>17.12839440703171</v>
       </c>
       <c r="R5">
-        <v>-104.2907188403053</v>
+        <v>-104.2907188403031</v>
       </c>
       <c r="S5">
-        <v>152.5232317990344</v>
+        <v>152.1628946803457</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -13783,58 +13783,58 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.8172794759706623</v>
+        <v>0.8192909477601665</v>
       </c>
       <c r="D6">
-        <v>0.7217366689642835</v>
+        <v>0.7477476736924514</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>9.437130509096363</v>
+        <v>9.460356984679116</v>
       </c>
       <c r="G6">
-        <v>8.333897202211057</v>
+        <v>8.634246413845066</v>
       </c>
       <c r="H6">
-        <v>10.07160052779999</v>
+        <v>7.614010012989719</v>
       </c>
       <c r="I6">
-        <v>7.079996444822623</v>
+        <v>6.446970466441317</v>
       </c>
       <c r="J6">
-        <v>3.953518728206193</v>
+        <v>3.953518728206214</v>
       </c>
       <c r="K6">
-        <v>6.198216755282932</v>
+        <v>6.198216755282955</v>
       </c>
       <c r="L6">
-        <v>3.953518728223953</v>
+        <v>3.953518728224016</v>
       </c>
       <c r="M6">
-        <v>6.19821675531351</v>
+        <v>6.198216755313494</v>
       </c>
       <c r="N6">
-        <v>0.8055518480312192</v>
+        <v>0.7946343373671535</v>
       </c>
       <c r="O6">
-        <v>0.4931849650005627</v>
+        <v>0.4931849650006355</v>
       </c>
       <c r="P6">
-        <v>0.7735594206637819</v>
+        <v>0.7609282792460932</v>
       </c>
       <c r="Q6">
-        <v>15.34097325496876</v>
+        <v>15.80538487780017</v>
       </c>
       <c r="R6">
-        <v>-96.35596491160986</v>
+        <v>-96.35596491160764</v>
       </c>
       <c r="S6">
-        <v>159.014630398495</v>
+        <v>158.917217550757</v>
       </c>
       <c r="T6">
-        <v>0.6571513103758266</v>
+        <v>0.717549443297119</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -13878,22 +13878,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>0.9063792352899561</v>
+        <v>0.8967513406455309</v>
       </c>
       <c r="O7">
-        <v>0.6518511244056876</v>
+        <v>0.651851124405757</v>
       </c>
       <c r="P7">
-        <v>0.7957851127634173</v>
+        <v>0.7871653857651081</v>
       </c>
       <c r="Q7">
-        <v>16.96787656741729</v>
+        <v>17.12839440928086</v>
       </c>
       <c r="R7">
-        <v>-104.2907188297765</v>
+        <v>-104.2907188297744</v>
       </c>
       <c r="S7">
-        <v>152.523231804048</v>
+        <v>152.1628946856566</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -13940,22 +13940,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0.9063792352899561</v>
+        <v>0.8967513406455307</v>
       </c>
       <c r="O8">
-        <v>0.6518511244056876</v>
+        <v>0.651851124405757</v>
       </c>
       <c r="P8">
-        <v>0.7957851127634173</v>
+        <v>0.7871653857651082</v>
       </c>
       <c r="Q8">
-        <v>16.9678765674173</v>
+        <v>17.12839440928086</v>
       </c>
       <c r="R8">
-        <v>-104.2907188297765</v>
+        <v>-104.2907188297744</v>
       </c>
       <c r="S8">
-        <v>152.523231804048</v>
+        <v>152.1628946856566</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -14002,22 +14002,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.8055518479482852</v>
+        <v>0.7946343372874243</v>
       </c>
       <c r="O9">
-        <v>0.4931849649794133</v>
+        <v>0.4931849649794861</v>
       </c>
       <c r="P9">
-        <v>0.773559420726195</v>
+        <v>0.760928279308372</v>
       </c>
       <c r="Q9">
-        <v>15.34097325963534</v>
+        <v>15.80538488283764</v>
       </c>
       <c r="R9">
-        <v>-96.35596489078564</v>
+        <v>-96.35596489078344</v>
       </c>
       <c r="S9">
-        <v>159.0146304036402</v>
+        <v>158.9172175563322</v>
       </c>
       <c r="T9">
         <v>0</v>
@@ -15218,22 +15218,22 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.07630958169751</v>
+        <v>1.076309581697509</v>
       </c>
       <c r="O2">
-        <v>0.3968725684451602</v>
+        <v>0.3968725684451616</v>
       </c>
       <c r="P2">
-        <v>0.857503166648943</v>
+        <v>0.8575031666489434</v>
       </c>
       <c r="Q2">
-        <v>8.789108950209512</v>
+        <v>8.789108950209521</v>
       </c>
       <c r="R2">
-        <v>-124.0274590207982</v>
+        <v>-124.027459020798</v>
       </c>
       <c r="S2">
-        <v>168.942911686649</v>
+        <v>168.9429116866489</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -15277,22 +15277,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.044105714997499</v>
+        <v>1.044105714997498</v>
       </c>
       <c r="O3">
-        <v>0.2604212734074322</v>
+        <v>0.2604212734074335</v>
       </c>
       <c r="P3">
-        <v>0.8710642653707255</v>
+        <v>0.871064265370725</v>
       </c>
       <c r="Q3">
-        <v>5.325452027459391</v>
+        <v>5.325452027459406</v>
       </c>
       <c r="R3">
-        <v>-131.9071155621095</v>
+        <v>-131.9071155621091</v>
       </c>
       <c r="S3">
-        <v>173.612583968783</v>
+        <v>173.6125839687828</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -15339,19 +15339,19 @@
         <v>1.044105714978375</v>
       </c>
       <c r="O4">
-        <v>0.2604212734211511</v>
+        <v>0.2604212734211526</v>
       </c>
       <c r="P4">
-        <v>0.8710642653956993</v>
+        <v>0.871064265395699</v>
       </c>
       <c r="Q4">
-        <v>5.325452029148323</v>
+        <v>5.325452029148344</v>
       </c>
       <c r="R4">
-        <v>-131.9071155464534</v>
+        <v>-131.907115546453</v>
       </c>
       <c r="S4">
-        <v>173.612583967056</v>
+        <v>173.6125839670559</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -15398,19 +15398,19 @@
         <v>1.044105714978375</v>
       </c>
       <c r="O5">
-        <v>0.260421273421151</v>
+        <v>0.2604212734211527</v>
       </c>
       <c r="P5">
-        <v>0.8710642653956993</v>
+        <v>0.8710642653956989</v>
       </c>
       <c r="Q5">
-        <v>5.325452029148323</v>
+        <v>5.325452029148344</v>
       </c>
       <c r="R5">
-        <v>-131.9071155464534</v>
+        <v>-131.907115546453</v>
       </c>
       <c r="S5">
-        <v>173.612583967056</v>
+        <v>173.6125839670559</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -15421,55 +15421,55 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>1.823703257666276</v>
+        <v>1.823703257666275</v>
       </c>
       <c r="D6">
-        <v>1.823703257666276</v>
+        <v>1.823703257666275</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>21.05831133471244</v>
+        <v>21.05831133471242</v>
       </c>
       <c r="G6">
-        <v>21.05831133471244</v>
+        <v>21.05831133471242</v>
       </c>
       <c r="H6">
-        <v>5.424025632034033</v>
+        <v>4.144030571481053</v>
       </c>
       <c r="I6">
-        <v>6.488939310918609</v>
+        <v>5.855913331295389</v>
       </c>
       <c r="J6">
-        <v>2.237816431607131</v>
+        <v>2.237816431607153</v>
       </c>
       <c r="K6">
-        <v>5.601194464564823</v>
+        <v>5.601194464564863</v>
       </c>
       <c r="L6">
-        <v>2.237816431580051</v>
+        <v>2.23781643158009</v>
       </c>
       <c r="M6">
-        <v>5.601194464517764</v>
+        <v>5.601194464517768</v>
       </c>
       <c r="N6">
-        <v>0.9526279648094362</v>
+        <v>0.9526279648094357</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.9526279648098424</v>
+        <v>0.9526279648098417</v>
       </c>
       <c r="Q6">
-        <v>-3.023660515913254E-13</v>
+        <v>-2.995790172241298E-13</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
       <c r="S6">
-        <v>179.9999999999921</v>
+        <v>179.999999999992</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -15513,22 +15513,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1.044105714823766</v>
+        <v>1.044105714823765</v>
       </c>
       <c r="O7">
-        <v>0.2604212731948773</v>
+        <v>0.2604212731948788</v>
       </c>
       <c r="P7">
-        <v>0.8710642655471983</v>
+        <v>0.8710642655471981</v>
       </c>
       <c r="Q7">
-        <v>5.325452029177773</v>
+        <v>5.325452029177791</v>
       </c>
       <c r="R7">
-        <v>-131.9071155000848</v>
+        <v>-131.9071155000844</v>
       </c>
       <c r="S7">
-        <v>173.612583969086</v>
+        <v>173.6125839690858</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -15572,22 +15572,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>1.044105714823766</v>
+        <v>1.044105714823765</v>
       </c>
       <c r="O8">
-        <v>0.2604212731948775</v>
+        <v>0.2604212731948792</v>
       </c>
       <c r="P8">
-        <v>0.8710642655471983</v>
+        <v>0.8710642655471981</v>
       </c>
       <c r="Q8">
-        <v>5.325452029177777</v>
+        <v>5.325452029177803</v>
       </c>
       <c r="R8">
-        <v>-131.9071155000848</v>
+        <v>-131.9071155000843</v>
       </c>
       <c r="S8">
-        <v>173.612583969086</v>
+        <v>173.6125839690858</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -15631,22 +15631,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>0.9526279646260468</v>
+        <v>0.9526279646260463</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.9526279649932319</v>
+        <v>0.9526279649932312</v>
       </c>
       <c r="Q9">
-        <v>1.108250066434003E-09</v>
+        <v>1.108252853468301E-09</v>
       </c>
       <c r="R9">
         <v>0</v>
       </c>
       <c r="S9">
-        <v>179.9999999988835</v>
+        <v>179.9999999988834</v>
       </c>
     </row>
   </sheetData>
